--- a/data/raw/Democracy in Action/review/dia_2012_organizations_review.xlsx
+++ b/data/raw/Democracy in Action/review/dia_2012_organizations_review.xlsx
@@ -9,17 +9,23 @@
     <sheet name="review" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'review'!$A$1:$Q$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'review'!$A$1:$S$43</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="238">
   <si>
     <t xml:space="preserve">row_id</t>
   </si>
   <si>
+    <t xml:space="preserve">review_action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">review_note</t>
+  </si>
+  <si>
     <t xml:space="preserve">contest_id</t>
   </si>
   <si>
@@ -69,6 +75,9 @@
   </si>
   <si>
     <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">2012D</t>
@@ -1065,22 +1074,24 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="15.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="40.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="23.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="21.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="8.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="10.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="10.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="8.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="18.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="18.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="40.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="11.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="80.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="14.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="40.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="8.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="8.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="15.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="40.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="23.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="21.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="8.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="10.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="10.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="8.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="18.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="18.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="40.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="11.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="80.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,1727 +1146,1985 @@
       <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
-        <v>24</v>
-      </c>
+      <c r="K2" s="1"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="N2" s="1"/>
-      <c r="O2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
       <c r="Q2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>32</v>
+      <c r="S3" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
       <c r="Q4" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J5" s="1"/>
-      <c r="K5" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="K5" s="1"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
+      <c r="M5" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="N5" s="1"/>
-      <c r="O5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
       <c r="Q5" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J6" s="1"/>
-      <c r="K6" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="K6" s="1"/>
       <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+      <c r="M6" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N6" s="1"/>
-      <c r="O6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
       <c r="Q6" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J7" s="1"/>
-      <c r="K7" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="K7" s="1"/>
       <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
+      <c r="M7" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="N7" s="1"/>
-      <c r="O7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
       <c r="Q7" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J8" s="1"/>
-      <c r="K8" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="K8" s="1"/>
       <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
+      <c r="M8" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="N8" s="1"/>
-      <c r="O8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
       <c r="Q8" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J9" s="1"/>
-      <c r="K9" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="K9" s="1"/>
       <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+      <c r="M9" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="N9" s="1"/>
-      <c r="O9" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
       <c r="Q9" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J10" s="1"/>
-      <c r="K10" s="1" t="s">
-        <v>65</v>
-      </c>
+      <c r="K10" s="1"/>
       <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
+      <c r="M10" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="N10" s="1"/>
-      <c r="O10" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
       <c r="Q10" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J11" s="1"/>
-      <c r="K11" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="K11" s="1"/>
       <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
+      <c r="M11" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="N11" s="1"/>
-      <c r="O11" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
       <c r="Q11" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J12" s="1"/>
-      <c r="K12" s="1" t="s">
-        <v>75</v>
-      </c>
+      <c r="K12" s="1"/>
       <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
+      <c r="M12" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="N12" s="1"/>
-      <c r="O12" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J13" s="1"/>
-      <c r="K13" s="1" t="s">
-        <v>80</v>
-      </c>
+      <c r="K13" s="1"/>
       <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
+      <c r="M13" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="N13" s="1"/>
-      <c r="O13" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
       <c r="Q13" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J14" s="1"/>
-      <c r="K14" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="K14" s="1"/>
       <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
+      <c r="M14" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="N14" s="1"/>
-      <c r="O14" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="P14" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
       <c r="Q14" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J15" s="1"/>
-      <c r="K15" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="K15" s="1"/>
       <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="N15" s="1"/>
-      <c r="O15" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
       <c r="Q15" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J16" s="1"/>
-      <c r="K16" s="1" t="s">
-        <v>95</v>
-      </c>
+      <c r="K16" s="1"/>
       <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
+      <c r="M16" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="N16" s="1"/>
-      <c r="O16" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
       <c r="Q16" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J17" s="1"/>
-      <c r="K17" s="1" t="s">
-        <v>100</v>
-      </c>
+      <c r="K17" s="1"/>
       <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
+      <c r="M17" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="N17" s="1"/>
-      <c r="O17" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
       <c r="Q17" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>104</v>
+        <v>23</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J18" s="1"/>
-      <c r="K18" s="1" t="s">
-        <v>105</v>
-      </c>
+      <c r="K18" s="1"/>
       <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
+      <c r="M18" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="N18" s="1"/>
-      <c r="O18" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
       <c r="Q18" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J19" s="1"/>
-      <c r="K19" s="1" t="s">
-        <v>110</v>
-      </c>
+      <c r="K19" s="1"/>
       <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
+      <c r="M19" s="1" t="s">
+        <v>113</v>
+      </c>
       <c r="N19" s="1"/>
-      <c r="O19" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
       <c r="Q19" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J20" s="1"/>
-      <c r="K20" s="1" t="s">
-        <v>115</v>
-      </c>
+      <c r="K20" s="1"/>
       <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
+      <c r="M20" s="1" t="s">
+        <v>118</v>
+      </c>
       <c r="N20" s="1"/>
-      <c r="O20" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
       <c r="Q20" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J21" s="1"/>
-      <c r="K21" s="1" t="s">
-        <v>120</v>
-      </c>
+      <c r="K21" s="1"/>
       <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
+      <c r="M21" s="1" t="s">
+        <v>123</v>
+      </c>
       <c r="N21" s="1"/>
-      <c r="O21" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
       <c r="Q21" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>124</v>
+        <v>23</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J22" s="1"/>
-      <c r="K22" s="1" t="s">
-        <v>125</v>
-      </c>
+      <c r="K22" s="1"/>
       <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
+      <c r="M22" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="N22" s="1"/>
-      <c r="O22" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
       <c r="Q22" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J23" s="1"/>
-      <c r="K23" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="K23" s="1"/>
       <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
+      <c r="M23" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="N23" s="1"/>
-      <c r="O23" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
       <c r="Q23" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>134</v>
+        <v>23</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J24" s="1"/>
-      <c r="K24" s="1" t="s">
-        <v>135</v>
-      </c>
+      <c r="K24" s="1"/>
       <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
+      <c r="M24" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="N24" s="1"/>
-      <c r="O24" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
       <c r="Q24" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>139</v>
+        <v>23</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J25" s="1"/>
-      <c r="K25" s="1" t="s">
-        <v>140</v>
-      </c>
+      <c r="K25" s="1"/>
       <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
+      <c r="M25" s="1" t="s">
+        <v>143</v>
+      </c>
       <c r="N25" s="1"/>
-      <c r="O25" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="P25" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
       <c r="Q25" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>144</v>
+        <v>23</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J26" s="1"/>
-      <c r="K26" s="1" t="s">
-        <v>145</v>
-      </c>
+      <c r="K26" s="1"/>
       <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
+      <c r="M26" s="1" t="s">
+        <v>148</v>
+      </c>
       <c r="N26" s="1"/>
-      <c r="O26" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
       <c r="Q26" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>149</v>
+        <v>23</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J27" s="1"/>
-      <c r="K27" s="1" t="s">
-        <v>150</v>
-      </c>
+      <c r="K27" s="1"/>
       <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
+      <c r="M27" s="1" t="s">
+        <v>153</v>
+      </c>
       <c r="N27" s="1"/>
-      <c r="O27" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="P27" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
       <c r="Q27" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J28" s="1"/>
-      <c r="K28" s="1" t="s">
-        <v>155</v>
-      </c>
+      <c r="K28" s="1"/>
       <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
+      <c r="M28" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="N28" s="1"/>
-      <c r="O28" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="P28" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
       <c r="Q28" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>159</v>
+        <v>23</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J29" s="1"/>
-      <c r="K29" s="1" t="s">
-        <v>160</v>
-      </c>
+      <c r="K29" s="1"/>
       <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
+      <c r="M29" s="1" t="s">
+        <v>163</v>
+      </c>
       <c r="N29" s="1"/>
-      <c r="O29" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="P29" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
       <c r="Q29" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>164</v>
+        <v>23</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J30" s="1"/>
-      <c r="K30" s="1" t="s">
-        <v>165</v>
-      </c>
+      <c r="K30" s="1"/>
       <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
+      <c r="M30" s="1" t="s">
+        <v>168</v>
+      </c>
       <c r="N30" s="1"/>
-      <c r="O30" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
       <c r="Q30" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>169</v>
+        <v>23</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J31" s="1"/>
-      <c r="K31" s="1" t="s">
-        <v>170</v>
-      </c>
+      <c r="K31" s="1"/>
       <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
+      <c r="M31" s="1" t="s">
+        <v>173</v>
+      </c>
       <c r="N31" s="1"/>
-      <c r="O31" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="P31" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
       <c r="Q31" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>174</v>
+        <v>23</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J32" s="1"/>
-      <c r="K32" s="1" t="s">
-        <v>175</v>
-      </c>
+      <c r="K32" s="1"/>
       <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
+      <c r="M32" s="1" t="s">
+        <v>178</v>
+      </c>
       <c r="N32" s="1"/>
-      <c r="O32" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
       <c r="Q32" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
+        <v>184</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J33" s="1"/>
-      <c r="K33" s="1" t="s">
-        <v>183</v>
-      </c>
+      <c r="K33" s="1"/>
       <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
+      <c r="M33" s="1" t="s">
+        <v>186</v>
+      </c>
       <c r="N33" s="1"/>
-      <c r="O33" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
       <c r="Q33" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
+        <v>184</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J34" s="1"/>
-      <c r="K34" s="1" t="s">
-        <v>188</v>
-      </c>
+      <c r="K34" s="1"/>
       <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
+      <c r="M34" s="1" t="s">
+        <v>191</v>
+      </c>
       <c r="N34" s="1"/>
-      <c r="O34" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="P34" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
       <c r="Q34" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
+        <v>184</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J35" s="1"/>
-      <c r="K35" s="1" t="s">
-        <v>193</v>
-      </c>
+      <c r="K35" s="1"/>
       <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
+      <c r="M35" s="1" t="s">
+        <v>196</v>
+      </c>
       <c r="N35" s="1"/>
-      <c r="O35" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="P35" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
       <c r="Q35" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
+        <v>184</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J36" s="1"/>
-      <c r="K36" s="1" t="s">
-        <v>198</v>
-      </c>
+      <c r="K36" s="1"/>
       <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
+      <c r="M36" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="N36" s="1"/>
-      <c r="O36" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
       <c r="Q36" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
+        <v>184</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J37" s="1"/>
-      <c r="K37" s="1" t="s">
-        <v>203</v>
-      </c>
+      <c r="K37" s="1"/>
       <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
+      <c r="M37" s="1" t="s">
+        <v>206</v>
+      </c>
       <c r="N37" s="1"/>
-      <c r="O37" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="P37" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
       <c r="Q37" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
       <c r="N38" s="1"/>
-      <c r="O38" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="P38" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
       <c r="Q38" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
+      </c>
+      <c r="R38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S38" s="1" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>211</v>
+        <v>183</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
+        <v>184</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J39" s="1"/>
-      <c r="K39" s="1" t="s">
-        <v>212</v>
-      </c>
+      <c r="K39" s="1"/>
       <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
+      <c r="M39" s="1" t="s">
+        <v>215</v>
+      </c>
       <c r="N39" s="1"/>
-      <c r="O39" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="P39" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
       <c r="Q39" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S39" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>216</v>
+        <v>183</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
+        <v>184</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J40" s="1"/>
-      <c r="K40" s="1" t="s">
-        <v>217</v>
-      </c>
+      <c r="K40" s="1"/>
       <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
+      <c r="M40" s="1" t="s">
+        <v>220</v>
+      </c>
       <c r="N40" s="1"/>
-      <c r="O40" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="P40" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
       <c r="Q40" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
+      </c>
+      <c r="R40" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S40" s="1" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>221</v>
+        <v>22</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>222</v>
+        <v>183</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
+        <v>224</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J41" s="1"/>
-      <c r="K41" s="1" t="s">
-        <v>223</v>
-      </c>
+      <c r="K41" s="1"/>
       <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
+      <c r="M41" s="1" t="s">
+        <v>226</v>
+      </c>
       <c r="N41" s="1"/>
-      <c r="O41" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
       <c r="Q41" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
+      </c>
+      <c r="R41" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S41" s="1" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>227</v>
+        <v>22</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
+        <v>230</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J42" s="1"/>
-      <c r="K42" s="1" t="s">
-        <v>228</v>
-      </c>
+      <c r="K42" s="1"/>
       <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
+      <c r="M42" s="1" t="s">
+        <v>231</v>
+      </c>
       <c r="N42" s="1"/>
-      <c r="O42" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="P42" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
       <c r="Q42" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S42" s="1" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>227</v>
+        <v>22</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
+        <v>230</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J43" s="1"/>
-      <c r="K43" s="1" t="s">
-        <v>232</v>
-      </c>
+      <c r="K43" s="1"/>
       <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
+      <c r="M43" s="1" t="s">
+        <v>235</v>
+      </c>
       <c r="N43" s="1"/>
-      <c r="O43" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="P43" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
       <c r="Q43" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S43" s="1" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="44">
@@ -2876,6 +3145,8 @@
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="1"/>
     </row>
     <row r="45">
       <c r="A45" s="1"/>
@@ -2895,6 +3166,8 @@
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
       <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
     </row>
     <row r="46">
       <c r="A46" s="1"/>
@@ -2914,6 +3187,8 @@
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
+      <c r="R46" s="1"/>
+      <c r="S46" s="1"/>
     </row>
     <row r="47">
       <c r="A47" s="1"/>
@@ -2933,6 +3208,8 @@
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
     </row>
     <row r="48">
       <c r="A48" s="1"/>
@@ -2952,6 +3229,8 @@
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+      <c r="S48" s="1"/>
     </row>
     <row r="49">
       <c r="A49" s="1"/>
@@ -2971,6 +3250,8 @@
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
+      <c r="S49" s="1"/>
     </row>
     <row r="50">
       <c r="A50" s="1"/>
@@ -2990,6 +3271,8 @@
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
       <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
+      <c r="S50" s="1"/>
     </row>
     <row r="51">
       <c r="A51" s="1"/>
@@ -3009,6 +3292,8 @@
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
       <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
     </row>
     <row r="52">
       <c r="A52" s="1"/>
@@ -3028,6 +3313,8 @@
       <c r="O52" s="1"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
+      <c r="R52" s="1"/>
+      <c r="S52" s="1"/>
     </row>
     <row r="53">
       <c r="A53" s="1"/>
@@ -3047,6 +3334,8 @@
       <c r="O53" s="1"/>
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
+      <c r="R53" s="1"/>
+      <c r="S53" s="1"/>
     </row>
     <row r="54">
       <c r="A54" s="1"/>
@@ -3066,6 +3355,8 @@
       <c r="O54" s="1"/>
       <c r="P54" s="1"/>
       <c r="Q54" s="1"/>
+      <c r="R54" s="1"/>
+      <c r="S54" s="1"/>
     </row>
     <row r="55">
       <c r="A55" s="1"/>
@@ -3085,6 +3376,8 @@
       <c r="O55" s="1"/>
       <c r="P55" s="1"/>
       <c r="Q55" s="1"/>
+      <c r="R55" s="1"/>
+      <c r="S55" s="1"/>
     </row>
     <row r="56">
       <c r="A56" s="1"/>
@@ -3104,6 +3397,8 @@
       <c r="O56" s="1"/>
       <c r="P56" s="1"/>
       <c r="Q56" s="1"/>
+      <c r="R56" s="1"/>
+      <c r="S56" s="1"/>
     </row>
     <row r="57">
       <c r="A57" s="1"/>
@@ -3123,6 +3418,8 @@
       <c r="O57" s="1"/>
       <c r="P57" s="1"/>
       <c r="Q57" s="1"/>
+      <c r="R57" s="1"/>
+      <c r="S57" s="1"/>
     </row>
     <row r="58">
       <c r="A58" s="1"/>
@@ -3142,6 +3439,8 @@
       <c r="O58" s="1"/>
       <c r="P58" s="1"/>
       <c r="Q58" s="1"/>
+      <c r="R58" s="1"/>
+      <c r="S58" s="1"/>
     </row>
     <row r="59">
       <c r="A59" s="1"/>
@@ -3161,6 +3460,8 @@
       <c r="O59" s="1"/>
       <c r="P59" s="1"/>
       <c r="Q59" s="1"/>
+      <c r="R59" s="1"/>
+      <c r="S59" s="1"/>
     </row>
     <row r="60">
       <c r="A60" s="1"/>
@@ -3180,6 +3481,8 @@
       <c r="O60" s="1"/>
       <c r="P60" s="1"/>
       <c r="Q60" s="1"/>
+      <c r="R60" s="1"/>
+      <c r="S60" s="1"/>
     </row>
     <row r="61">
       <c r="A61" s="1"/>
@@ -3199,6 +3502,8 @@
       <c r="O61" s="1"/>
       <c r="P61" s="1"/>
       <c r="Q61" s="1"/>
+      <c r="R61" s="1"/>
+      <c r="S61" s="1"/>
     </row>
     <row r="62">
       <c r="A62" s="1"/>
@@ -3218,6 +3523,8 @@
       <c r="O62" s="1"/>
       <c r="P62" s="1"/>
       <c r="Q62" s="1"/>
+      <c r="R62" s="1"/>
+      <c r="S62" s="1"/>
     </row>
     <row r="63">
       <c r="A63" s="1"/>
@@ -3237,6 +3544,8 @@
       <c r="O63" s="1"/>
       <c r="P63" s="1"/>
       <c r="Q63" s="1"/>
+      <c r="R63" s="1"/>
+      <c r="S63" s="1"/>
     </row>
     <row r="64">
       <c r="A64" s="1"/>
@@ -3256,6 +3565,8 @@
       <c r="O64" s="1"/>
       <c r="P64" s="1"/>
       <c r="Q64" s="1"/>
+      <c r="R64" s="1"/>
+      <c r="S64" s="1"/>
     </row>
     <row r="65">
       <c r="A65" s="1"/>
@@ -3275,6 +3586,8 @@
       <c r="O65" s="1"/>
       <c r="P65" s="1"/>
       <c r="Q65" s="1"/>
+      <c r="R65" s="1"/>
+      <c r="S65" s="1"/>
     </row>
     <row r="66">
       <c r="A66" s="1"/>
@@ -3294,6 +3607,8 @@
       <c r="O66" s="1"/>
       <c r="P66" s="1"/>
       <c r="Q66" s="1"/>
+      <c r="R66" s="1"/>
+      <c r="S66" s="1"/>
     </row>
     <row r="67">
       <c r="A67" s="1"/>
@@ -3313,6 +3628,8 @@
       <c r="O67" s="1"/>
       <c r="P67" s="1"/>
       <c r="Q67" s="1"/>
+      <c r="R67" s="1"/>
+      <c r="S67" s="1"/>
     </row>
     <row r="68">
       <c r="A68" s="1"/>
@@ -3332,6 +3649,8 @@
       <c r="O68" s="1"/>
       <c r="P68" s="1"/>
       <c r="Q68" s="1"/>
+      <c r="R68" s="1"/>
+      <c r="S68" s="1"/>
     </row>
     <row r="69">
       <c r="A69" s="1"/>
@@ -3351,6 +3670,8 @@
       <c r="O69" s="1"/>
       <c r="P69" s="1"/>
       <c r="Q69" s="1"/>
+      <c r="R69" s="1"/>
+      <c r="S69" s="1"/>
     </row>
     <row r="70">
       <c r="A70" s="1"/>
@@ -3370,6 +3691,8 @@
       <c r="O70" s="1"/>
       <c r="P70" s="1"/>
       <c r="Q70" s="1"/>
+      <c r="R70" s="1"/>
+      <c r="S70" s="1"/>
     </row>
     <row r="71">
       <c r="A71" s="1"/>
@@ -3389,6 +3712,8 @@
       <c r="O71" s="1"/>
       <c r="P71" s="1"/>
       <c r="Q71" s="1"/>
+      <c r="R71" s="1"/>
+      <c r="S71" s="1"/>
     </row>
     <row r="72">
       <c r="A72" s="1"/>
@@ -3408,6 +3733,8 @@
       <c r="O72" s="1"/>
       <c r="P72" s="1"/>
       <c r="Q72" s="1"/>
+      <c r="R72" s="1"/>
+      <c r="S72" s="1"/>
     </row>
     <row r="73">
       <c r="A73" s="1"/>
@@ -3427,6 +3754,8 @@
       <c r="O73" s="1"/>
       <c r="P73" s="1"/>
       <c r="Q73" s="1"/>
+      <c r="R73" s="1"/>
+      <c r="S73" s="1"/>
     </row>
     <row r="74">
       <c r="A74" s="1"/>
@@ -3446,6 +3775,8 @@
       <c r="O74" s="1"/>
       <c r="P74" s="1"/>
       <c r="Q74" s="1"/>
+      <c r="R74" s="1"/>
+      <c r="S74" s="1"/>
     </row>
     <row r="75">
       <c r="A75" s="1"/>
@@ -3465,6 +3796,8 @@
       <c r="O75" s="1"/>
       <c r="P75" s="1"/>
       <c r="Q75" s="1"/>
+      <c r="R75" s="1"/>
+      <c r="S75" s="1"/>
     </row>
     <row r="76">
       <c r="A76" s="1"/>
@@ -3484,6 +3817,8 @@
       <c r="O76" s="1"/>
       <c r="P76" s="1"/>
       <c r="Q76" s="1"/>
+      <c r="R76" s="1"/>
+      <c r="S76" s="1"/>
     </row>
     <row r="77">
       <c r="A77" s="1"/>
@@ -3503,6 +3838,8 @@
       <c r="O77" s="1"/>
       <c r="P77" s="1"/>
       <c r="Q77" s="1"/>
+      <c r="R77" s="1"/>
+      <c r="S77" s="1"/>
     </row>
     <row r="78">
       <c r="A78" s="1"/>
@@ -3522,6 +3859,8 @@
       <c r="O78" s="1"/>
       <c r="P78" s="1"/>
       <c r="Q78" s="1"/>
+      <c r="R78" s="1"/>
+      <c r="S78" s="1"/>
     </row>
     <row r="79">
       <c r="A79" s="1"/>
@@ -3541,6 +3880,8 @@
       <c r="O79" s="1"/>
       <c r="P79" s="1"/>
       <c r="Q79" s="1"/>
+      <c r="R79" s="1"/>
+      <c r="S79" s="1"/>
     </row>
     <row r="80">
       <c r="A80" s="1"/>
@@ -3560,6 +3901,8 @@
       <c r="O80" s="1"/>
       <c r="P80" s="1"/>
       <c r="Q80" s="1"/>
+      <c r="R80" s="1"/>
+      <c r="S80" s="1"/>
     </row>
     <row r="81">
       <c r="A81" s="1"/>
@@ -3579,6 +3922,8 @@
       <c r="O81" s="1"/>
       <c r="P81" s="1"/>
       <c r="Q81" s="1"/>
+      <c r="R81" s="1"/>
+      <c r="S81" s="1"/>
     </row>
     <row r="82">
       <c r="A82" s="1"/>
@@ -3598,6 +3943,8 @@
       <c r="O82" s="1"/>
       <c r="P82" s="1"/>
       <c r="Q82" s="1"/>
+      <c r="R82" s="1"/>
+      <c r="S82" s="1"/>
     </row>
     <row r="83">
       <c r="A83" s="1"/>
@@ -3617,6 +3964,8 @@
       <c r="O83" s="1"/>
       <c r="P83" s="1"/>
       <c r="Q83" s="1"/>
+      <c r="R83" s="1"/>
+      <c r="S83" s="1"/>
     </row>
     <row r="84">
       <c r="A84" s="1"/>
@@ -3636,6 +3985,8 @@
       <c r="O84" s="1"/>
       <c r="P84" s="1"/>
       <c r="Q84" s="1"/>
+      <c r="R84" s="1"/>
+      <c r="S84" s="1"/>
     </row>
     <row r="85">
       <c r="A85" s="1"/>
@@ -3655,6 +4006,8 @@
       <c r="O85" s="1"/>
       <c r="P85" s="1"/>
       <c r="Q85" s="1"/>
+      <c r="R85" s="1"/>
+      <c r="S85" s="1"/>
     </row>
     <row r="86">
       <c r="A86" s="1"/>
@@ -3674,6 +4027,8 @@
       <c r="O86" s="1"/>
       <c r="P86" s="1"/>
       <c r="Q86" s="1"/>
+      <c r="R86" s="1"/>
+      <c r="S86" s="1"/>
     </row>
     <row r="87">
       <c r="A87" s="1"/>
@@ -3693,6 +4048,8 @@
       <c r="O87" s="1"/>
       <c r="P87" s="1"/>
       <c r="Q87" s="1"/>
+      <c r="R87" s="1"/>
+      <c r="S87" s="1"/>
     </row>
     <row r="88">
       <c r="A88" s="1"/>
@@ -3712,6 +4069,8 @@
       <c r="O88" s="1"/>
       <c r="P88" s="1"/>
       <c r="Q88" s="1"/>
+      <c r="R88" s="1"/>
+      <c r="S88" s="1"/>
     </row>
     <row r="89">
       <c r="A89" s="1"/>
@@ -3731,6 +4090,8 @@
       <c r="O89" s="1"/>
       <c r="P89" s="1"/>
       <c r="Q89" s="1"/>
+      <c r="R89" s="1"/>
+      <c r="S89" s="1"/>
     </row>
     <row r="90">
       <c r="A90" s="1"/>
@@ -3750,6 +4111,8 @@
       <c r="O90" s="1"/>
       <c r="P90" s="1"/>
       <c r="Q90" s="1"/>
+      <c r="R90" s="1"/>
+      <c r="S90" s="1"/>
     </row>
     <row r="91">
       <c r="A91" s="1"/>
@@ -3769,6 +4132,8 @@
       <c r="O91" s="1"/>
       <c r="P91" s="1"/>
       <c r="Q91" s="1"/>
+      <c r="R91" s="1"/>
+      <c r="S91" s="1"/>
     </row>
     <row r="92">
       <c r="A92" s="1"/>
@@ -3788,6 +4153,8 @@
       <c r="O92" s="1"/>
       <c r="P92" s="1"/>
       <c r="Q92" s="1"/>
+      <c r="R92" s="1"/>
+      <c r="S92" s="1"/>
     </row>
     <row r="93">
       <c r="A93" s="1"/>
@@ -3807,6 +4174,8 @@
       <c r="O93" s="1"/>
       <c r="P93" s="1"/>
       <c r="Q93" s="1"/>
+      <c r="R93" s="1"/>
+      <c r="S93" s="1"/>
     </row>
     <row r="94">
       <c r="A94" s="1"/>
@@ -3826,6 +4195,8 @@
       <c r="O94" s="1"/>
       <c r="P94" s="1"/>
       <c r="Q94" s="1"/>
+      <c r="R94" s="1"/>
+      <c r="S94" s="1"/>
     </row>
     <row r="95">
       <c r="A95" s="1"/>
@@ -3845,6 +4216,8 @@
       <c r="O95" s="1"/>
       <c r="P95" s="1"/>
       <c r="Q95" s="1"/>
+      <c r="R95" s="1"/>
+      <c r="S95" s="1"/>
     </row>
     <row r="96">
       <c r="A96" s="1"/>
@@ -3864,6 +4237,8 @@
       <c r="O96" s="1"/>
       <c r="P96" s="1"/>
       <c r="Q96" s="1"/>
+      <c r="R96" s="1"/>
+      <c r="S96" s="1"/>
     </row>
     <row r="97">
       <c r="A97" s="1"/>
@@ -3883,6 +4258,8 @@
       <c r="O97" s="1"/>
       <c r="P97" s="1"/>
       <c r="Q97" s="1"/>
+      <c r="R97" s="1"/>
+      <c r="S97" s="1"/>
     </row>
     <row r="98">
       <c r="A98" s="1"/>
@@ -3902,6 +4279,8 @@
       <c r="O98" s="1"/>
       <c r="P98" s="1"/>
       <c r="Q98" s="1"/>
+      <c r="R98" s="1"/>
+      <c r="S98" s="1"/>
     </row>
     <row r="99">
       <c r="A99" s="1"/>
@@ -3921,6 +4300,8 @@
       <c r="O99" s="1"/>
       <c r="P99" s="1"/>
       <c r="Q99" s="1"/>
+      <c r="R99" s="1"/>
+      <c r="S99" s="1"/>
     </row>
     <row r="100">
       <c r="A100" s="1"/>
@@ -3940,6 +4321,8 @@
       <c r="O100" s="1"/>
       <c r="P100" s="1"/>
       <c r="Q100" s="1"/>
+      <c r="R100" s="1"/>
+      <c r="S100" s="1"/>
     </row>
     <row r="101">
       <c r="A101" s="1"/>
@@ -3959,6 +4342,8 @@
       <c r="O101" s="1"/>
       <c r="P101" s="1"/>
       <c r="Q101" s="1"/>
+      <c r="R101" s="1"/>
+      <c r="S101" s="1"/>
     </row>
     <row r="102">
       <c r="A102" s="1"/>
@@ -3978,6 +4363,8 @@
       <c r="O102" s="1"/>
       <c r="P102" s="1"/>
       <c r="Q102" s="1"/>
+      <c r="R102" s="1"/>
+      <c r="S102" s="1"/>
     </row>
     <row r="103">
       <c r="A103" s="1"/>
@@ -3997,6 +4384,8 @@
       <c r="O103" s="1"/>
       <c r="P103" s="1"/>
       <c r="Q103" s="1"/>
+      <c r="R103" s="1"/>
+      <c r="S103" s="1"/>
     </row>
     <row r="104">
       <c r="A104" s="1"/>
@@ -4016,6 +4405,8 @@
       <c r="O104" s="1"/>
       <c r="P104" s="1"/>
       <c r="Q104" s="1"/>
+      <c r="R104" s="1"/>
+      <c r="S104" s="1"/>
     </row>
     <row r="105">
       <c r="A105" s="1"/>
@@ -4035,6 +4426,8 @@
       <c r="O105" s="1"/>
       <c r="P105" s="1"/>
       <c r="Q105" s="1"/>
+      <c r="R105" s="1"/>
+      <c r="S105" s="1"/>
     </row>
     <row r="106">
       <c r="A106" s="1"/>
@@ -4054,6 +4447,8 @@
       <c r="O106" s="1"/>
       <c r="P106" s="1"/>
       <c r="Q106" s="1"/>
+      <c r="R106" s="1"/>
+      <c r="S106" s="1"/>
     </row>
     <row r="107">
       <c r="A107" s="1"/>
@@ -4073,6 +4468,8 @@
       <c r="O107" s="1"/>
       <c r="P107" s="1"/>
       <c r="Q107" s="1"/>
+      <c r="R107" s="1"/>
+      <c r="S107" s="1"/>
     </row>
     <row r="108">
       <c r="A108" s="1"/>
@@ -4092,6 +4489,8 @@
       <c r="O108" s="1"/>
       <c r="P108" s="1"/>
       <c r="Q108" s="1"/>
+      <c r="R108" s="1"/>
+      <c r="S108" s="1"/>
     </row>
     <row r="109">
       <c r="A109" s="1"/>
@@ -4111,6 +4510,8 @@
       <c r="O109" s="1"/>
       <c r="P109" s="1"/>
       <c r="Q109" s="1"/>
+      <c r="R109" s="1"/>
+      <c r="S109" s="1"/>
     </row>
     <row r="110">
       <c r="A110" s="1"/>
@@ -4130,6 +4531,8 @@
       <c r="O110" s="1"/>
       <c r="P110" s="1"/>
       <c r="Q110" s="1"/>
+      <c r="R110" s="1"/>
+      <c r="S110" s="1"/>
     </row>
     <row r="111">
       <c r="A111" s="1"/>
@@ -4149,6 +4552,8 @@
       <c r="O111" s="1"/>
       <c r="P111" s="1"/>
       <c r="Q111" s="1"/>
+      <c r="R111" s="1"/>
+      <c r="S111" s="1"/>
     </row>
     <row r="112">
       <c r="A112" s="1"/>
@@ -4168,6 +4573,8 @@
       <c r="O112" s="1"/>
       <c r="P112" s="1"/>
       <c r="Q112" s="1"/>
+      <c r="R112" s="1"/>
+      <c r="S112" s="1"/>
     </row>
     <row r="113">
       <c r="A113" s="1"/>
@@ -4187,6 +4594,8 @@
       <c r="O113" s="1"/>
       <c r="P113" s="1"/>
       <c r="Q113" s="1"/>
+      <c r="R113" s="1"/>
+      <c r="S113" s="1"/>
     </row>
     <row r="114">
       <c r="A114" s="1"/>
@@ -4206,6 +4615,8 @@
       <c r="O114" s="1"/>
       <c r="P114" s="1"/>
       <c r="Q114" s="1"/>
+      <c r="R114" s="1"/>
+      <c r="S114" s="1"/>
     </row>
     <row r="115">
       <c r="A115" s="1"/>
@@ -4225,6 +4636,8 @@
       <c r="O115" s="1"/>
       <c r="P115" s="1"/>
       <c r="Q115" s="1"/>
+      <c r="R115" s="1"/>
+      <c r="S115" s="1"/>
     </row>
     <row r="116">
       <c r="A116" s="1"/>
@@ -4244,6 +4657,8 @@
       <c r="O116" s="1"/>
       <c r="P116" s="1"/>
       <c r="Q116" s="1"/>
+      <c r="R116" s="1"/>
+      <c r="S116" s="1"/>
     </row>
     <row r="117">
       <c r="A117" s="1"/>
@@ -4263,6 +4678,8 @@
       <c r="O117" s="1"/>
       <c r="P117" s="1"/>
       <c r="Q117" s="1"/>
+      <c r="R117" s="1"/>
+      <c r="S117" s="1"/>
     </row>
     <row r="118">
       <c r="A118" s="1"/>
@@ -4282,6 +4699,8 @@
       <c r="O118" s="1"/>
       <c r="P118" s="1"/>
       <c r="Q118" s="1"/>
+      <c r="R118" s="1"/>
+      <c r="S118" s="1"/>
     </row>
     <row r="119">
       <c r="A119" s="1"/>
@@ -4301,6 +4720,8 @@
       <c r="O119" s="1"/>
       <c r="P119" s="1"/>
       <c r="Q119" s="1"/>
+      <c r="R119" s="1"/>
+      <c r="S119" s="1"/>
     </row>
     <row r="120">
       <c r="A120" s="1"/>
@@ -4320,6 +4741,8 @@
       <c r="O120" s="1"/>
       <c r="P120" s="1"/>
       <c r="Q120" s="1"/>
+      <c r="R120" s="1"/>
+      <c r="S120" s="1"/>
     </row>
     <row r="121">
       <c r="A121" s="1"/>
@@ -4339,6 +4762,8 @@
       <c r="O121" s="1"/>
       <c r="P121" s="1"/>
       <c r="Q121" s="1"/>
+      <c r="R121" s="1"/>
+      <c r="S121" s="1"/>
     </row>
     <row r="122">
       <c r="A122" s="1"/>
@@ -4358,6 +4783,8 @@
       <c r="O122" s="1"/>
       <c r="P122" s="1"/>
       <c r="Q122" s="1"/>
+      <c r="R122" s="1"/>
+      <c r="S122" s="1"/>
     </row>
     <row r="123">
       <c r="A123" s="1"/>
@@ -4377,6 +4804,8 @@
       <c r="O123" s="1"/>
       <c r="P123" s="1"/>
       <c r="Q123" s="1"/>
+      <c r="R123" s="1"/>
+      <c r="S123" s="1"/>
     </row>
     <row r="124">
       <c r="A124" s="1"/>
@@ -4396,6 +4825,8 @@
       <c r="O124" s="1"/>
       <c r="P124" s="1"/>
       <c r="Q124" s="1"/>
+      <c r="R124" s="1"/>
+      <c r="S124" s="1"/>
     </row>
     <row r="125">
       <c r="A125" s="1"/>
@@ -4415,6 +4846,8 @@
       <c r="O125" s="1"/>
       <c r="P125" s="1"/>
       <c r="Q125" s="1"/>
+      <c r="R125" s="1"/>
+      <c r="S125" s="1"/>
     </row>
     <row r="126">
       <c r="A126" s="1"/>
@@ -4434,6 +4867,8 @@
       <c r="O126" s="1"/>
       <c r="P126" s="1"/>
       <c r="Q126" s="1"/>
+      <c r="R126" s="1"/>
+      <c r="S126" s="1"/>
     </row>
     <row r="127">
       <c r="A127" s="1"/>
@@ -4453,6 +4888,8 @@
       <c r="O127" s="1"/>
       <c r="P127" s="1"/>
       <c r="Q127" s="1"/>
+      <c r="R127" s="1"/>
+      <c r="S127" s="1"/>
     </row>
     <row r="128">
       <c r="A128" s="1"/>
@@ -4472,6 +4909,8 @@
       <c r="O128" s="1"/>
       <c r="P128" s="1"/>
       <c r="Q128" s="1"/>
+      <c r="R128" s="1"/>
+      <c r="S128" s="1"/>
     </row>
     <row r="129">
       <c r="A129" s="1"/>
@@ -4491,6 +4930,8 @@
       <c r="O129" s="1"/>
       <c r="P129" s="1"/>
       <c r="Q129" s="1"/>
+      <c r="R129" s="1"/>
+      <c r="S129" s="1"/>
     </row>
     <row r="130">
       <c r="A130" s="1"/>
@@ -4510,6 +4951,8 @@
       <c r="O130" s="1"/>
       <c r="P130" s="1"/>
       <c r="Q130" s="1"/>
+      <c r="R130" s="1"/>
+      <c r="S130" s="1"/>
     </row>
     <row r="131">
       <c r="A131" s="1"/>
@@ -4529,6 +4972,8 @@
       <c r="O131" s="1"/>
       <c r="P131" s="1"/>
       <c r="Q131" s="1"/>
+      <c r="R131" s="1"/>
+      <c r="S131" s="1"/>
     </row>
     <row r="132">
       <c r="A132" s="1"/>
@@ -4548,6 +4993,8 @@
       <c r="O132" s="1"/>
       <c r="P132" s="1"/>
       <c r="Q132" s="1"/>
+      <c r="R132" s="1"/>
+      <c r="S132" s="1"/>
     </row>
     <row r="133">
       <c r="A133" s="1"/>
@@ -4567,6 +5014,8 @@
       <c r="O133" s="1"/>
       <c r="P133" s="1"/>
       <c r="Q133" s="1"/>
+      <c r="R133" s="1"/>
+      <c r="S133" s="1"/>
     </row>
     <row r="134">
       <c r="A134" s="1"/>
@@ -4586,6 +5035,8 @@
       <c r="O134" s="1"/>
       <c r="P134" s="1"/>
       <c r="Q134" s="1"/>
+      <c r="R134" s="1"/>
+      <c r="S134" s="1"/>
     </row>
     <row r="135">
       <c r="A135" s="1"/>
@@ -4605,6 +5056,8 @@
       <c r="O135" s="1"/>
       <c r="P135" s="1"/>
       <c r="Q135" s="1"/>
+      <c r="R135" s="1"/>
+      <c r="S135" s="1"/>
     </row>
     <row r="136">
       <c r="A136" s="1"/>
@@ -4624,6 +5077,8 @@
       <c r="O136" s="1"/>
       <c r="P136" s="1"/>
       <c r="Q136" s="1"/>
+      <c r="R136" s="1"/>
+      <c r="S136" s="1"/>
     </row>
     <row r="137">
       <c r="A137" s="1"/>
@@ -4643,6 +5098,8 @@
       <c r="O137" s="1"/>
       <c r="P137" s="1"/>
       <c r="Q137" s="1"/>
+      <c r="R137" s="1"/>
+      <c r="S137" s="1"/>
     </row>
     <row r="138">
       <c r="A138" s="1"/>
@@ -4662,6 +5119,8 @@
       <c r="O138" s="1"/>
       <c r="P138" s="1"/>
       <c r="Q138" s="1"/>
+      <c r="R138" s="1"/>
+      <c r="S138" s="1"/>
     </row>
     <row r="139">
       <c r="A139" s="1"/>
@@ -4681,6 +5140,8 @@
       <c r="O139" s="1"/>
       <c r="P139" s="1"/>
       <c r="Q139" s="1"/>
+      <c r="R139" s="1"/>
+      <c r="S139" s="1"/>
     </row>
     <row r="140">
       <c r="A140" s="1"/>
@@ -4700,6 +5161,8 @@
       <c r="O140" s="1"/>
       <c r="P140" s="1"/>
       <c r="Q140" s="1"/>
+      <c r="R140" s="1"/>
+      <c r="S140" s="1"/>
     </row>
     <row r="141">
       <c r="A141" s="1"/>
@@ -4719,6 +5182,8 @@
       <c r="O141" s="1"/>
       <c r="P141" s="1"/>
       <c r="Q141" s="1"/>
+      <c r="R141" s="1"/>
+      <c r="S141" s="1"/>
     </row>
     <row r="142">
       <c r="A142" s="1"/>
@@ -4738,6 +5203,8 @@
       <c r="O142" s="1"/>
       <c r="P142" s="1"/>
       <c r="Q142" s="1"/>
+      <c r="R142" s="1"/>
+      <c r="S142" s="1"/>
     </row>
     <row r="143">
       <c r="A143" s="1"/>
@@ -4757,6 +5224,8 @@
       <c r="O143" s="1"/>
       <c r="P143" s="1"/>
       <c r="Q143" s="1"/>
+      <c r="R143" s="1"/>
+      <c r="S143" s="1"/>
     </row>
     <row r="144">
       <c r="A144" s="1"/>
@@ -4776,6 +5245,8 @@
       <c r="O144" s="1"/>
       <c r="P144" s="1"/>
       <c r="Q144" s="1"/>
+      <c r="R144" s="1"/>
+      <c r="S144" s="1"/>
     </row>
     <row r="145">
       <c r="A145" s="1"/>
@@ -4795,6 +5266,8 @@
       <c r="O145" s="1"/>
       <c r="P145" s="1"/>
       <c r="Q145" s="1"/>
+      <c r="R145" s="1"/>
+      <c r="S145" s="1"/>
     </row>
     <row r="146">
       <c r="A146" s="1"/>
@@ -4814,6 +5287,8 @@
       <c r="O146" s="1"/>
       <c r="P146" s="1"/>
       <c r="Q146" s="1"/>
+      <c r="R146" s="1"/>
+      <c r="S146" s="1"/>
     </row>
     <row r="147">
       <c r="A147" s="1"/>
@@ -4833,6 +5308,8 @@
       <c r="O147" s="1"/>
       <c r="P147" s="1"/>
       <c r="Q147" s="1"/>
+      <c r="R147" s="1"/>
+      <c r="S147" s="1"/>
     </row>
     <row r="148">
       <c r="A148" s="1"/>
@@ -4852,6 +5329,8 @@
       <c r="O148" s="1"/>
       <c r="P148" s="1"/>
       <c r="Q148" s="1"/>
+      <c r="R148" s="1"/>
+      <c r="S148" s="1"/>
     </row>
     <row r="149">
       <c r="A149" s="1"/>
@@ -4871,6 +5350,8 @@
       <c r="O149" s="1"/>
       <c r="P149" s="1"/>
       <c r="Q149" s="1"/>
+      <c r="R149" s="1"/>
+      <c r="S149" s="1"/>
     </row>
     <row r="150">
       <c r="A150" s="1"/>
@@ -4890,6 +5371,8 @@
       <c r="O150" s="1"/>
       <c r="P150" s="1"/>
       <c r="Q150" s="1"/>
+      <c r="R150" s="1"/>
+      <c r="S150" s="1"/>
     </row>
     <row r="151">
       <c r="A151" s="1"/>
@@ -4909,6 +5392,8 @@
       <c r="O151" s="1"/>
       <c r="P151" s="1"/>
       <c r="Q151" s="1"/>
+      <c r="R151" s="1"/>
+      <c r="S151" s="1"/>
     </row>
     <row r="152">
       <c r="A152" s="1"/>
@@ -4928,6 +5413,8 @@
       <c r="O152" s="1"/>
       <c r="P152" s="1"/>
       <c r="Q152" s="1"/>
+      <c r="R152" s="1"/>
+      <c r="S152" s="1"/>
     </row>
     <row r="153">
       <c r="A153" s="1"/>
@@ -4947,6 +5434,8 @@
       <c r="O153" s="1"/>
       <c r="P153" s="1"/>
       <c r="Q153" s="1"/>
+      <c r="R153" s="1"/>
+      <c r="S153" s="1"/>
     </row>
     <row r="154">
       <c r="A154" s="1"/>
@@ -4966,6 +5455,8 @@
       <c r="O154" s="1"/>
       <c r="P154" s="1"/>
       <c r="Q154" s="1"/>
+      <c r="R154" s="1"/>
+      <c r="S154" s="1"/>
     </row>
     <row r="155">
       <c r="A155" s="1"/>
@@ -4985,6 +5476,8 @@
       <c r="O155" s="1"/>
       <c r="P155" s="1"/>
       <c r="Q155" s="1"/>
+      <c r="R155" s="1"/>
+      <c r="S155" s="1"/>
     </row>
     <row r="156">
       <c r="A156" s="1"/>
@@ -5004,6 +5497,8 @@
       <c r="O156" s="1"/>
       <c r="P156" s="1"/>
       <c r="Q156" s="1"/>
+      <c r="R156" s="1"/>
+      <c r="S156" s="1"/>
     </row>
     <row r="157">
       <c r="A157" s="1"/>
@@ -5023,6 +5518,8 @@
       <c r="O157" s="1"/>
       <c r="P157" s="1"/>
       <c r="Q157" s="1"/>
+      <c r="R157" s="1"/>
+      <c r="S157" s="1"/>
     </row>
     <row r="158">
       <c r="A158" s="1"/>
@@ -5042,6 +5539,8 @@
       <c r="O158" s="1"/>
       <c r="P158" s="1"/>
       <c r="Q158" s="1"/>
+      <c r="R158" s="1"/>
+      <c r="S158" s="1"/>
     </row>
     <row r="159">
       <c r="A159" s="1"/>
@@ -5061,6 +5560,8 @@
       <c r="O159" s="1"/>
       <c r="P159" s="1"/>
       <c r="Q159" s="1"/>
+      <c r="R159" s="1"/>
+      <c r="S159" s="1"/>
     </row>
     <row r="160">
       <c r="A160" s="1"/>
@@ -5080,6 +5581,8 @@
       <c r="O160" s="1"/>
       <c r="P160" s="1"/>
       <c r="Q160" s="1"/>
+      <c r="R160" s="1"/>
+      <c r="S160" s="1"/>
     </row>
     <row r="161">
       <c r="A161" s="1"/>
@@ -5099,6 +5602,8 @@
       <c r="O161" s="1"/>
       <c r="P161" s="1"/>
       <c r="Q161" s="1"/>
+      <c r="R161" s="1"/>
+      <c r="S161" s="1"/>
     </row>
     <row r="162">
       <c r="A162" s="1"/>
@@ -5118,6 +5623,8 @@
       <c r="O162" s="1"/>
       <c r="P162" s="1"/>
       <c r="Q162" s="1"/>
+      <c r="R162" s="1"/>
+      <c r="S162" s="1"/>
     </row>
     <row r="163">
       <c r="A163" s="1"/>
@@ -5137,6 +5644,8 @@
       <c r="O163" s="1"/>
       <c r="P163" s="1"/>
       <c r="Q163" s="1"/>
+      <c r="R163" s="1"/>
+      <c r="S163" s="1"/>
     </row>
     <row r="164">
       <c r="A164" s="1"/>
@@ -5156,6 +5665,8 @@
       <c r="O164" s="1"/>
       <c r="P164" s="1"/>
       <c r="Q164" s="1"/>
+      <c r="R164" s="1"/>
+      <c r="S164" s="1"/>
     </row>
     <row r="165">
       <c r="A165" s="1"/>
@@ -5175,6 +5686,8 @@
       <c r="O165" s="1"/>
       <c r="P165" s="1"/>
       <c r="Q165" s="1"/>
+      <c r="R165" s="1"/>
+      <c r="S165" s="1"/>
     </row>
     <row r="166">
       <c r="A166" s="1"/>
@@ -5194,6 +5707,8 @@
       <c r="O166" s="1"/>
       <c r="P166" s="1"/>
       <c r="Q166" s="1"/>
+      <c r="R166" s="1"/>
+      <c r="S166" s="1"/>
     </row>
     <row r="167">
       <c r="A167" s="1"/>
@@ -5213,6 +5728,8 @@
       <c r="O167" s="1"/>
       <c r="P167" s="1"/>
       <c r="Q167" s="1"/>
+      <c r="R167" s="1"/>
+      <c r="S167" s="1"/>
     </row>
     <row r="168">
       <c r="A168" s="1"/>
@@ -5232,6 +5749,8 @@
       <c r="O168" s="1"/>
       <c r="P168" s="1"/>
       <c r="Q168" s="1"/>
+      <c r="R168" s="1"/>
+      <c r="S168" s="1"/>
     </row>
     <row r="169">
       <c r="A169" s="1"/>
@@ -5251,6 +5770,8 @@
       <c r="O169" s="1"/>
       <c r="P169" s="1"/>
       <c r="Q169" s="1"/>
+      <c r="R169" s="1"/>
+      <c r="S169" s="1"/>
     </row>
     <row r="170">
       <c r="A170" s="1"/>
@@ -5270,6 +5791,8 @@
       <c r="O170" s="1"/>
       <c r="P170" s="1"/>
       <c r="Q170" s="1"/>
+      <c r="R170" s="1"/>
+      <c r="S170" s="1"/>
     </row>
     <row r="171">
       <c r="A171" s="1"/>
@@ -5289,6 +5812,8 @@
       <c r="O171" s="1"/>
       <c r="P171" s="1"/>
       <c r="Q171" s="1"/>
+      <c r="R171" s="1"/>
+      <c r="S171" s="1"/>
     </row>
     <row r="172">
       <c r="A172" s="1"/>
@@ -5308,6 +5833,8 @@
       <c r="O172" s="1"/>
       <c r="P172" s="1"/>
       <c r="Q172" s="1"/>
+      <c r="R172" s="1"/>
+      <c r="S172" s="1"/>
     </row>
     <row r="173">
       <c r="A173" s="1"/>
@@ -5327,6 +5854,8 @@
       <c r="O173" s="1"/>
       <c r="P173" s="1"/>
       <c r="Q173" s="1"/>
+      <c r="R173" s="1"/>
+      <c r="S173" s="1"/>
     </row>
     <row r="174">
       <c r="A174" s="1"/>
@@ -5346,6 +5875,8 @@
       <c r="O174" s="1"/>
       <c r="P174" s="1"/>
       <c r="Q174" s="1"/>
+      <c r="R174" s="1"/>
+      <c r="S174" s="1"/>
     </row>
     <row r="175">
       <c r="A175" s="1"/>
@@ -5365,6 +5896,8 @@
       <c r="O175" s="1"/>
       <c r="P175" s="1"/>
       <c r="Q175" s="1"/>
+      <c r="R175" s="1"/>
+      <c r="S175" s="1"/>
     </row>
     <row r="176">
       <c r="A176" s="1"/>
@@ -5384,6 +5917,8 @@
       <c r="O176" s="1"/>
       <c r="P176" s="1"/>
       <c r="Q176" s="1"/>
+      <c r="R176" s="1"/>
+      <c r="S176" s="1"/>
     </row>
     <row r="177">
       <c r="A177" s="1"/>
@@ -5403,6 +5938,8 @@
       <c r="O177" s="1"/>
       <c r="P177" s="1"/>
       <c r="Q177" s="1"/>
+      <c r="R177" s="1"/>
+      <c r="S177" s="1"/>
     </row>
     <row r="178">
       <c r="A178" s="1"/>
@@ -5422,6 +5959,8 @@
       <c r="O178" s="1"/>
       <c r="P178" s="1"/>
       <c r="Q178" s="1"/>
+      <c r="R178" s="1"/>
+      <c r="S178" s="1"/>
     </row>
     <row r="179">
       <c r="A179" s="1"/>
@@ -5441,6 +5980,8 @@
       <c r="O179" s="1"/>
       <c r="P179" s="1"/>
       <c r="Q179" s="1"/>
+      <c r="R179" s="1"/>
+      <c r="S179" s="1"/>
     </row>
     <row r="180">
       <c r="A180" s="1"/>
@@ -5460,6 +6001,8 @@
       <c r="O180" s="1"/>
       <c r="P180" s="1"/>
       <c r="Q180" s="1"/>
+      <c r="R180" s="1"/>
+      <c r="S180" s="1"/>
     </row>
     <row r="181">
       <c r="A181" s="1"/>
@@ -5479,6 +6022,8 @@
       <c r="O181" s="1"/>
       <c r="P181" s="1"/>
       <c r="Q181" s="1"/>
+      <c r="R181" s="1"/>
+      <c r="S181" s="1"/>
     </row>
     <row r="182">
       <c r="A182" s="1"/>
@@ -5498,6 +6043,8 @@
       <c r="O182" s="1"/>
       <c r="P182" s="1"/>
       <c r="Q182" s="1"/>
+      <c r="R182" s="1"/>
+      <c r="S182" s="1"/>
     </row>
     <row r="183">
       <c r="A183" s="1"/>
@@ -5517,6 +6064,8 @@
       <c r="O183" s="1"/>
       <c r="P183" s="1"/>
       <c r="Q183" s="1"/>
+      <c r="R183" s="1"/>
+      <c r="S183" s="1"/>
     </row>
     <row r="184">
       <c r="A184" s="1"/>
@@ -5536,6 +6085,8 @@
       <c r="O184" s="1"/>
       <c r="P184" s="1"/>
       <c r="Q184" s="1"/>
+      <c r="R184" s="1"/>
+      <c r="S184" s="1"/>
     </row>
     <row r="185">
       <c r="A185" s="1"/>
@@ -5555,6 +6106,8 @@
       <c r="O185" s="1"/>
       <c r="P185" s="1"/>
       <c r="Q185" s="1"/>
+      <c r="R185" s="1"/>
+      <c r="S185" s="1"/>
     </row>
     <row r="186">
       <c r="A186" s="1"/>
@@ -5574,6 +6127,8 @@
       <c r="O186" s="1"/>
       <c r="P186" s="1"/>
       <c r="Q186" s="1"/>
+      <c r="R186" s="1"/>
+      <c r="S186" s="1"/>
     </row>
     <row r="187">
       <c r="A187" s="1"/>
@@ -5593,6 +6148,8 @@
       <c r="O187" s="1"/>
       <c r="P187" s="1"/>
       <c r="Q187" s="1"/>
+      <c r="R187" s="1"/>
+      <c r="S187" s="1"/>
     </row>
     <row r="188">
       <c r="A188" s="1"/>
@@ -5612,6 +6169,8 @@
       <c r="O188" s="1"/>
       <c r="P188" s="1"/>
       <c r="Q188" s="1"/>
+      <c r="R188" s="1"/>
+      <c r="S188" s="1"/>
     </row>
     <row r="189">
       <c r="A189" s="1"/>
@@ -5631,6 +6190,8 @@
       <c r="O189" s="1"/>
       <c r="P189" s="1"/>
       <c r="Q189" s="1"/>
+      <c r="R189" s="1"/>
+      <c r="S189" s="1"/>
     </row>
     <row r="190">
       <c r="A190" s="1"/>
@@ -5650,6 +6211,8 @@
       <c r="O190" s="1"/>
       <c r="P190" s="1"/>
       <c r="Q190" s="1"/>
+      <c r="R190" s="1"/>
+      <c r="S190" s="1"/>
     </row>
     <row r="191">
       <c r="A191" s="1"/>
@@ -5669,6 +6232,8 @@
       <c r="O191" s="1"/>
       <c r="P191" s="1"/>
       <c r="Q191" s="1"/>
+      <c r="R191" s="1"/>
+      <c r="S191" s="1"/>
     </row>
     <row r="192">
       <c r="A192" s="1"/>
@@ -5688,6 +6253,8 @@
       <c r="O192" s="1"/>
       <c r="P192" s="1"/>
       <c r="Q192" s="1"/>
+      <c r="R192" s="1"/>
+      <c r="S192" s="1"/>
     </row>
     <row r="193">
       <c r="A193" s="1"/>
@@ -5707,6 +6274,8 @@
       <c r="O193" s="1"/>
       <c r="P193" s="1"/>
       <c r="Q193" s="1"/>
+      <c r="R193" s="1"/>
+      <c r="S193" s="1"/>
     </row>
     <row r="194">
       <c r="A194" s="1"/>
@@ -5726,6 +6295,8 @@
       <c r="O194" s="1"/>
       <c r="P194" s="1"/>
       <c r="Q194" s="1"/>
+      <c r="R194" s="1"/>
+      <c r="S194" s="1"/>
     </row>
     <row r="195">
       <c r="A195" s="1"/>
@@ -5745,6 +6316,8 @@
       <c r="O195" s="1"/>
       <c r="P195" s="1"/>
       <c r="Q195" s="1"/>
+      <c r="R195" s="1"/>
+      <c r="S195" s="1"/>
     </row>
     <row r="196">
       <c r="A196" s="1"/>
@@ -5764,6 +6337,8 @@
       <c r="O196" s="1"/>
       <c r="P196" s="1"/>
       <c r="Q196" s="1"/>
+      <c r="R196" s="1"/>
+      <c r="S196" s="1"/>
     </row>
     <row r="197">
       <c r="A197" s="1"/>
@@ -5783,6 +6358,8 @@
       <c r="O197" s="1"/>
       <c r="P197" s="1"/>
       <c r="Q197" s="1"/>
+      <c r="R197" s="1"/>
+      <c r="S197" s="1"/>
     </row>
     <row r="198">
       <c r="A198" s="1"/>
@@ -5802,6 +6379,8 @@
       <c r="O198" s="1"/>
       <c r="P198" s="1"/>
       <c r="Q198" s="1"/>
+      <c r="R198" s="1"/>
+      <c r="S198" s="1"/>
     </row>
     <row r="199">
       <c r="A199" s="1"/>
@@ -5821,6 +6400,8 @@
       <c r="O199" s="1"/>
       <c r="P199" s="1"/>
       <c r="Q199" s="1"/>
+      <c r="R199" s="1"/>
+      <c r="S199" s="1"/>
     </row>
     <row r="200">
       <c r="A200" s="1"/>
@@ -5840,6 +6421,8 @@
       <c r="O200" s="1"/>
       <c r="P200" s="1"/>
       <c r="Q200" s="1"/>
+      <c r="R200" s="1"/>
+      <c r="S200" s="1"/>
     </row>
     <row r="201">
       <c r="A201" s="1"/>
@@ -5859,6 +6442,8 @@
       <c r="O201" s="1"/>
       <c r="P201" s="1"/>
       <c r="Q201" s="1"/>
+      <c r="R201" s="1"/>
+      <c r="S201" s="1"/>
     </row>
     <row r="202">
       <c r="A202" s="1"/>
@@ -5878,6 +6463,8 @@
       <c r="O202" s="1"/>
       <c r="P202" s="1"/>
       <c r="Q202" s="1"/>
+      <c r="R202" s="1"/>
+      <c r="S202" s="1"/>
     </row>
     <row r="203">
       <c r="A203" s="1"/>
@@ -5897,6 +6484,8 @@
       <c r="O203" s="1"/>
       <c r="P203" s="1"/>
       <c r="Q203" s="1"/>
+      <c r="R203" s="1"/>
+      <c r="S203" s="1"/>
     </row>
     <row r="204">
       <c r="A204" s="1"/>
@@ -5916,6 +6505,8 @@
       <c r="O204" s="1"/>
       <c r="P204" s="1"/>
       <c r="Q204" s="1"/>
+      <c r="R204" s="1"/>
+      <c r="S204" s="1"/>
     </row>
     <row r="205">
       <c r="A205" s="1"/>
@@ -5935,6 +6526,8 @@
       <c r="O205" s="1"/>
       <c r="P205" s="1"/>
       <c r="Q205" s="1"/>
+      <c r="R205" s="1"/>
+      <c r="S205" s="1"/>
     </row>
     <row r="206">
       <c r="A206" s="1"/>
@@ -5954,6 +6547,8 @@
       <c r="O206" s="1"/>
       <c r="P206" s="1"/>
       <c r="Q206" s="1"/>
+      <c r="R206" s="1"/>
+      <c r="S206" s="1"/>
     </row>
     <row r="207">
       <c r="A207" s="1"/>
@@ -5973,6 +6568,8 @@
       <c r="O207" s="1"/>
       <c r="P207" s="1"/>
       <c r="Q207" s="1"/>
+      <c r="R207" s="1"/>
+      <c r="S207" s="1"/>
     </row>
     <row r="208">
       <c r="A208" s="1"/>
@@ -5992,6 +6589,8 @@
       <c r="O208" s="1"/>
       <c r="P208" s="1"/>
       <c r="Q208" s="1"/>
+      <c r="R208" s="1"/>
+      <c r="S208" s="1"/>
     </row>
     <row r="209">
       <c r="A209" s="1"/>
@@ -6011,6 +6610,8 @@
       <c r="O209" s="1"/>
       <c r="P209" s="1"/>
       <c r="Q209" s="1"/>
+      <c r="R209" s="1"/>
+      <c r="S209" s="1"/>
     </row>
     <row r="210">
       <c r="A210" s="1"/>
@@ -6030,6 +6631,8 @@
       <c r="O210" s="1"/>
       <c r="P210" s="1"/>
       <c r="Q210" s="1"/>
+      <c r="R210" s="1"/>
+      <c r="S210" s="1"/>
     </row>
     <row r="211">
       <c r="A211" s="1"/>
@@ -6049,6 +6652,8 @@
       <c r="O211" s="1"/>
       <c r="P211" s="1"/>
       <c r="Q211" s="1"/>
+      <c r="R211" s="1"/>
+      <c r="S211" s="1"/>
     </row>
     <row r="212">
       <c r="A212" s="1"/>
@@ -6068,6 +6673,8 @@
       <c r="O212" s="1"/>
       <c r="P212" s="1"/>
       <c r="Q212" s="1"/>
+      <c r="R212" s="1"/>
+      <c r="S212" s="1"/>
     </row>
     <row r="213">
       <c r="A213" s="1"/>
@@ -6087,6 +6694,8 @@
       <c r="O213" s="1"/>
       <c r="P213" s="1"/>
       <c r="Q213" s="1"/>
+      <c r="R213" s="1"/>
+      <c r="S213" s="1"/>
     </row>
     <row r="214">
       <c r="A214" s="1"/>
@@ -6106,6 +6715,8 @@
       <c r="O214" s="1"/>
       <c r="P214" s="1"/>
       <c r="Q214" s="1"/>
+      <c r="R214" s="1"/>
+      <c r="S214" s="1"/>
     </row>
     <row r="215">
       <c r="A215" s="1"/>
@@ -6125,6 +6736,8 @@
       <c r="O215" s="1"/>
       <c r="P215" s="1"/>
       <c r="Q215" s="1"/>
+      <c r="R215" s="1"/>
+      <c r="S215" s="1"/>
     </row>
     <row r="216">
       <c r="A216" s="1"/>
@@ -6144,6 +6757,8 @@
       <c r="O216" s="1"/>
       <c r="P216" s="1"/>
       <c r="Q216" s="1"/>
+      <c r="R216" s="1"/>
+      <c r="S216" s="1"/>
     </row>
     <row r="217">
       <c r="A217" s="1"/>
@@ -6163,6 +6778,8 @@
       <c r="O217" s="1"/>
       <c r="P217" s="1"/>
       <c r="Q217" s="1"/>
+      <c r="R217" s="1"/>
+      <c r="S217" s="1"/>
     </row>
     <row r="218">
       <c r="A218" s="1"/>
@@ -6182,6 +6799,8 @@
       <c r="O218" s="1"/>
       <c r="P218" s="1"/>
       <c r="Q218" s="1"/>
+      <c r="R218" s="1"/>
+      <c r="S218" s="1"/>
     </row>
     <row r="219">
       <c r="A219" s="1"/>
@@ -6201,6 +6820,8 @@
       <c r="O219" s="1"/>
       <c r="P219" s="1"/>
       <c r="Q219" s="1"/>
+      <c r="R219" s="1"/>
+      <c r="S219" s="1"/>
     </row>
     <row r="220">
       <c r="A220" s="1"/>
@@ -6220,6 +6841,8 @@
       <c r="O220" s="1"/>
       <c r="P220" s="1"/>
       <c r="Q220" s="1"/>
+      <c r="R220" s="1"/>
+      <c r="S220" s="1"/>
     </row>
     <row r="221">
       <c r="A221" s="1"/>
@@ -6239,6 +6862,8 @@
       <c r="O221" s="1"/>
       <c r="P221" s="1"/>
       <c r="Q221" s="1"/>
+      <c r="R221" s="1"/>
+      <c r="S221" s="1"/>
     </row>
     <row r="222">
       <c r="A222" s="1"/>
@@ -6258,6 +6883,8 @@
       <c r="O222" s="1"/>
       <c r="P222" s="1"/>
       <c r="Q222" s="1"/>
+      <c r="R222" s="1"/>
+      <c r="S222" s="1"/>
     </row>
     <row r="223">
       <c r="A223" s="1"/>
@@ -6277,6 +6904,8 @@
       <c r="O223" s="1"/>
       <c r="P223" s="1"/>
       <c r="Q223" s="1"/>
+      <c r="R223" s="1"/>
+      <c r="S223" s="1"/>
     </row>
     <row r="224">
       <c r="A224" s="1"/>
@@ -6296,6 +6925,8 @@
       <c r="O224" s="1"/>
       <c r="P224" s="1"/>
       <c r="Q224" s="1"/>
+      <c r="R224" s="1"/>
+      <c r="S224" s="1"/>
     </row>
     <row r="225">
       <c r="A225" s="1"/>
@@ -6315,6 +6946,8 @@
       <c r="O225" s="1"/>
       <c r="P225" s="1"/>
       <c r="Q225" s="1"/>
+      <c r="R225" s="1"/>
+      <c r="S225" s="1"/>
     </row>
     <row r="226">
       <c r="A226" s="1"/>
@@ -6334,6 +6967,8 @@
       <c r="O226" s="1"/>
       <c r="P226" s="1"/>
       <c r="Q226" s="1"/>
+      <c r="R226" s="1"/>
+      <c r="S226" s="1"/>
     </row>
     <row r="227">
       <c r="A227" s="1"/>
@@ -6353,6 +6988,8 @@
       <c r="O227" s="1"/>
       <c r="P227" s="1"/>
       <c r="Q227" s="1"/>
+      <c r="R227" s="1"/>
+      <c r="S227" s="1"/>
     </row>
     <row r="228">
       <c r="A228" s="1"/>
@@ -6372,6 +7009,8 @@
       <c r="O228" s="1"/>
       <c r="P228" s="1"/>
       <c r="Q228" s="1"/>
+      <c r="R228" s="1"/>
+      <c r="S228" s="1"/>
     </row>
     <row r="229">
       <c r="A229" s="1"/>
@@ -6391,6 +7030,8 @@
       <c r="O229" s="1"/>
       <c r="P229" s="1"/>
       <c r="Q229" s="1"/>
+      <c r="R229" s="1"/>
+      <c r="S229" s="1"/>
     </row>
     <row r="230">
       <c r="A230" s="1"/>
@@ -6410,6 +7051,8 @@
       <c r="O230" s="1"/>
       <c r="P230" s="1"/>
       <c r="Q230" s="1"/>
+      <c r="R230" s="1"/>
+      <c r="S230" s="1"/>
     </row>
     <row r="231">
       <c r="A231" s="1"/>
@@ -6429,6 +7072,8 @@
       <c r="O231" s="1"/>
       <c r="P231" s="1"/>
       <c r="Q231" s="1"/>
+      <c r="R231" s="1"/>
+      <c r="S231" s="1"/>
     </row>
     <row r="232">
       <c r="A232" s="1"/>
@@ -6448,6 +7093,8 @@
       <c r="O232" s="1"/>
       <c r="P232" s="1"/>
       <c r="Q232" s="1"/>
+      <c r="R232" s="1"/>
+      <c r="S232" s="1"/>
     </row>
     <row r="233">
       <c r="A233" s="1"/>
@@ -6467,6 +7114,8 @@
       <c r="O233" s="1"/>
       <c r="P233" s="1"/>
       <c r="Q233" s="1"/>
+      <c r="R233" s="1"/>
+      <c r="S233" s="1"/>
     </row>
     <row r="234">
       <c r="A234" s="1"/>
@@ -6486,6 +7135,8 @@
       <c r="O234" s="1"/>
       <c r="P234" s="1"/>
       <c r="Q234" s="1"/>
+      <c r="R234" s="1"/>
+      <c r="S234" s="1"/>
     </row>
     <row r="235">
       <c r="A235" s="1"/>
@@ -6505,6 +7156,8 @@
       <c r="O235" s="1"/>
       <c r="P235" s="1"/>
       <c r="Q235" s="1"/>
+      <c r="R235" s="1"/>
+      <c r="S235" s="1"/>
     </row>
     <row r="236">
       <c r="A236" s="1"/>
@@ -6524,6 +7177,8 @@
       <c r="O236" s="1"/>
       <c r="P236" s="1"/>
       <c r="Q236" s="1"/>
+      <c r="R236" s="1"/>
+      <c r="S236" s="1"/>
     </row>
     <row r="237">
       <c r="A237" s="1"/>
@@ -6543,6 +7198,8 @@
       <c r="O237" s="1"/>
       <c r="P237" s="1"/>
       <c r="Q237" s="1"/>
+      <c r="R237" s="1"/>
+      <c r="S237" s="1"/>
     </row>
     <row r="238">
       <c r="A238" s="1"/>
@@ -6562,6 +7219,8 @@
       <c r="O238" s="1"/>
       <c r="P238" s="1"/>
       <c r="Q238" s="1"/>
+      <c r="R238" s="1"/>
+      <c r="S238" s="1"/>
     </row>
     <row r="239">
       <c r="A239" s="1"/>
@@ -6581,6 +7240,8 @@
       <c r="O239" s="1"/>
       <c r="P239" s="1"/>
       <c r="Q239" s="1"/>
+      <c r="R239" s="1"/>
+      <c r="S239" s="1"/>
     </row>
     <row r="240">
       <c r="A240" s="1"/>
@@ -6600,6 +7261,8 @@
       <c r="O240" s="1"/>
       <c r="P240" s="1"/>
       <c r="Q240" s="1"/>
+      <c r="R240" s="1"/>
+      <c r="S240" s="1"/>
     </row>
     <row r="241">
       <c r="A241" s="1"/>
@@ -6619,6 +7282,8 @@
       <c r="O241" s="1"/>
       <c r="P241" s="1"/>
       <c r="Q241" s="1"/>
+      <c r="R241" s="1"/>
+      <c r="S241" s="1"/>
     </row>
     <row r="242">
       <c r="A242" s="1"/>
@@ -6638,6 +7303,8 @@
       <c r="O242" s="1"/>
       <c r="P242" s="1"/>
       <c r="Q242" s="1"/>
+      <c r="R242" s="1"/>
+      <c r="S242" s="1"/>
     </row>
     <row r="243">
       <c r="A243" s="1"/>
@@ -6657,9 +7324,11 @@
       <c r="O243" s="1"/>
       <c r="P243" s="1"/>
       <c r="Q243" s="1"/>
+      <c r="R243" s="1"/>
+      <c r="S243" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q43"/>
+  <autoFilter ref="A1:S43"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/data/raw/Democracy in Action/review/dia_2012_organizations_review.xlsx
+++ b/data/raw/Democracy in Action/review/dia_2012_organizations_review.xlsx
@@ -1,745 +1,782 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/katherineparslow/Documents/repos/presidential-endorsements/data/raw/Democracy in Action/review/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF1C602-ABE1-5E49-8F3A-CC7E2B4572FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="review" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="review" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'review'!$A$1:$S$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">review!$A$1:$S$46</definedName>
   </definedNames>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="238">
-  <si>
-    <t xml:space="preserve">row_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">review_action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">review_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contest_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">party</t>
-  </si>
-  <si>
-    <t xml:space="preserve">endorsee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">endorser_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">endorser_description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">endorser_party_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">district</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date_raw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">switch_direction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">switch_candidate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evidence_url</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parsed_ok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">raw_text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">2012D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barack Obama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Association of Police Organizations (NAPO)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Organization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/25/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">napo072512.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Association of Police Organizations (NAPO) 07/25/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feminist Majority</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/11/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feministmajority071112pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feminist Majority 07/11/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Organization for Women PAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nowpac071112pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Organization for Women PAC 07/11/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MoveOn Political Action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/21/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">moveon062112pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MoveOn Political Action 06/21/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planned Parenthood Action Fund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/30/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ppaf053012pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planned Parenthood Action Fund 05/30/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NARAL Pro Choice America PAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/15/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">naral051512pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NARAL Pro Choice America PAC 05/15/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sierra Club, League of Conservation Voters, Environment Action, Clean Water Action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/18/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">env041812pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sierra Club, League of Conservation Voters, Environment Action, Clean Water Action 04/18/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human Rights Campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/26/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hrcpac052611pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human Rights Campaign 05/26/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flight Attendants Union Coalition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Labor Union</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/27/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fauc092712pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flight Attendants Union Coalition 09/27/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Postal Workers Union (APWU)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/22/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apwu082212.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Postal Workers Union (APWU) 08/22/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Association of Fire Fighters (IAFF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/08/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iaff060812pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Association of Fire Fighters (IAFF) 06/08/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Federation of Government Employees (AFGE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/10/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">afge0612email.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Federation of Government Employees (AFGE) 05/10/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Brotherhood of Teamsters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/07/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">teamsters050712pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Brotherhood of Teamsters 05/07/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Building and Construction Trades Department, AFL-CIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/01/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">buildingtrades050112pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Building and Construction Trades Department, AFL-CIO 05/01/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Union of Bricklayers and Allied Craftworkers (BAC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/24/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bac042412pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Union of Bricklayers and Allied Craftworkers (BAC) 04/24/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Federation of School Administrators (AFSA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/22/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">afsa050912pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Federation of School Administrators (AFSA) 04/22/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bakery, Confectionery, Tobacco Workers and Grain Millers (BCTGM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/05/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bctgm040512pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bakery, Confectionery, Tobacco Workers and Grain Millers (BCTGM) 04/05/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AFL-CIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03/13/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aflcio031312pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AFL-CIO 03/13/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Brotherhood of Boilermakers (IBB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03/09/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ibb030912pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Brotherhood of Boilermakers (IBB) 03/09/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laborers International Union of North America (LIUNA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03/08/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.p2012.org/interestg/liuna030812pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laborers International Union of North America (LIUNA) 03/08/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Steelworkers (USW)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03/06/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.p2012.org/interestg/usw030612pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Steelworkers (USW) 03/06/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Association of Journeymen and Apprentices of the Plumbing and Pipefitting Industry (UA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03/01/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ua030112pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Association of Journeymen and Apprentices of the Plumbing and Pipefitting Industry (UA) 03/01/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Association of Machinists (IAM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/24/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iam022412pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Association of Machinists (IAM) 02/24/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Federation of Teachers (AFT)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/07/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aft020712pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Federation of Teachers (AFT) 02/07/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communications Workers of America (CWA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/02/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cwa020212pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communications Workers of America (CWA) 02/02/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Farm Workers (UFW)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/12/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.p2012.org/interestg/ufw011212pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Farm Workers (UFW) 01/12/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Federation of State, County and Municipal Employees (AFSCME)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/06/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">afscme120611pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Federation of State, County and Municipal Employees (AFSCME) 12/06/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retail, Wholesale and Department Store Union UFCW (RWDSU)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/17/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../interestg/rwdsu111711pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retail, Wholesale and Department Store Union UFCW (RWDSU) 11/17/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Employees International Union (SEIU)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/16/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.p2012.org/interestg/seiu111611pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Employees International Union (SEIU) 11/16/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Food and Commercial Workers Union (UFCW)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/20/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ufcw102011pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Food and Commercial Workers Union (UFCW) 10/20/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Education Association (NEA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/04/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../interestg/nea070411pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Education Association (NEA) 07/04/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2012R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitt Romney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log Cabin Republicans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/23/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logcabin102312pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log Cabin Republicans 10/23/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Rifle Association Political Victory Fund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/04/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nrapvf100412pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Rifle Association Political Victory Fund 10/04/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CatholicVote.org</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/13/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">catholicvoteorg081312pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CatholicVote.org 08/13/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOProud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/20/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">goproud062012pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOProud 06/20/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Right to LIfe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/12/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nrtl041212pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Right to LIfe 04/12/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Susan B. Anthony List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sbalist041212pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Susan B. Anthony List 04/12/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Organization for Marriage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/11/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nom041112pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Organization for Marriage 04/11/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Associated Builders and Contractors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/22/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abc022212pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Associated Builders and Contractors 02/22/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Newt Gingrich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Campaign to Defeat Barack Obama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/29/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">campaigntodefeat012912pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Campaign to Defeat Barack Obama 01/29/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rick Santorum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/17/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sbalist021712pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Susan B. Anthony List 02/17/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/05/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">catholicvoteorg010512pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CatholicVote.org 01/05/12</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="249">
+  <si>
+    <t>row_id</t>
+  </si>
+  <si>
+    <t>review_action</t>
+  </si>
+  <si>
+    <t>review_note</t>
+  </si>
+  <si>
+    <t>contest_id</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>party</t>
+  </si>
+  <si>
+    <t>endorsee</t>
+  </si>
+  <si>
+    <t>endorser_name</t>
+  </si>
+  <si>
+    <t>endorser_description</t>
+  </si>
+  <si>
+    <t>endorser_party_note</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>district</t>
+  </si>
+  <si>
+    <t>date_raw</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>switch_direction</t>
+  </si>
+  <si>
+    <t>switch_candidate</t>
+  </si>
+  <si>
+    <t>evidence_url</t>
+  </si>
+  <si>
+    <t>parsed_ok</t>
+  </si>
+  <si>
+    <t>raw_text</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2012D</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Barack Obama</t>
+  </si>
+  <si>
+    <t>National Association of Police Organizations (NAPO)</t>
+  </si>
+  <si>
+    <t>National Organization</t>
+  </si>
+  <si>
+    <t>07/25/12</t>
+  </si>
+  <si>
+    <t>napo072512.html</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>National Association of Police Organizations (NAPO) 07/25/12</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Feminist Majority</t>
+  </si>
+  <si>
+    <t>07/11/12</t>
+  </si>
+  <si>
+    <t>feministmajority071112pr.html</t>
+  </si>
+  <si>
+    <t>Feminist Majority 07/11/12</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>National Organization for Women PAC</t>
+  </si>
+  <si>
+    <t>nowpac071112pr.html</t>
+  </si>
+  <si>
+    <t>National Organization for Women PAC 07/11/12</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>MoveOn Political Action</t>
+  </si>
+  <si>
+    <t>06/21/12</t>
+  </si>
+  <si>
+    <t>moveon062112pr.html</t>
+  </si>
+  <si>
+    <t>MoveOn Political Action 06/21/12</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Planned Parenthood Action Fund</t>
+  </si>
+  <si>
+    <t>05/30/12</t>
+  </si>
+  <si>
+    <t>ppaf053012pr.html</t>
+  </si>
+  <si>
+    <t>Planned Parenthood Action Fund 05/30/12</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>NARAL Pro Choice America PAC</t>
+  </si>
+  <si>
+    <t>05/15/12</t>
+  </si>
+  <si>
+    <t>naral051512pr.html</t>
+  </si>
+  <si>
+    <t>NARAL Pro Choice America PAC 05/15/12</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>04/18/12</t>
+  </si>
+  <si>
+    <t>env041812pr.html</t>
+  </si>
+  <si>
+    <t>Sierra Club, League of Conservation Voters, Environment Action, Clean Water Action 04/18/12</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Human Rights Campaign</t>
+  </si>
+  <si>
+    <t>05/26/11</t>
+  </si>
+  <si>
+    <t>hrcpac052611pr.html</t>
+  </si>
+  <si>
+    <t>Human Rights Campaign 05/26/11</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Flight Attendants Union Coalition</t>
+  </si>
+  <si>
+    <t>Labor Union</t>
+  </si>
+  <si>
+    <t>09/27/12</t>
+  </si>
+  <si>
+    <t>fauc092712pr.html</t>
+  </si>
+  <si>
+    <t>Flight Attendants Union Coalition 09/27/12</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>American Postal Workers Union (APWU)</t>
+  </si>
+  <si>
+    <t>08/22/12</t>
+  </si>
+  <si>
+    <t>apwu082212.html</t>
+  </si>
+  <si>
+    <t>American Postal Workers Union (APWU) 08/22/12</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>International Association of Fire Fighters (IAFF)</t>
+  </si>
+  <si>
+    <t>06/08/12</t>
+  </si>
+  <si>
+    <t>iaff060812pr.html</t>
+  </si>
+  <si>
+    <t>International Association of Fire Fighters (IAFF) 06/08/12</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>American Federation of Government Employees (AFGE)</t>
+  </si>
+  <si>
+    <t>05/10/12</t>
+  </si>
+  <si>
+    <t>afge0612email.html</t>
+  </si>
+  <si>
+    <t>American Federation of Government Employees (AFGE) 05/10/12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>International Brotherhood of Teamsters</t>
+  </si>
+  <si>
+    <t>05/07/12</t>
+  </si>
+  <si>
+    <t>teamsters050712pr.html</t>
+  </si>
+  <si>
+    <t>International Brotherhood of Teamsters 05/07/12</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Building and Construction Trades Department, AFL-CIO</t>
+  </si>
+  <si>
+    <t>05/01/12</t>
+  </si>
+  <si>
+    <t>buildingtrades050112pr.html</t>
+  </si>
+  <si>
+    <t>Building and Construction Trades Department, AFL-CIO 05/01/12</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>International Union of Bricklayers and Allied Craftworkers (BAC)</t>
+  </si>
+  <si>
+    <t>04/24/12</t>
+  </si>
+  <si>
+    <t>bac042412pr.html</t>
+  </si>
+  <si>
+    <t>International Union of Bricklayers and Allied Craftworkers (BAC) 04/24/12</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>American Federation of School Administrators (AFSA)</t>
+  </si>
+  <si>
+    <t>04/22/12</t>
+  </si>
+  <si>
+    <t>afsa050912pr.html</t>
+  </si>
+  <si>
+    <t>American Federation of School Administrators (AFSA) 04/22/12</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Bakery, Confectionery, Tobacco Workers and Grain Millers (BCTGM)</t>
+  </si>
+  <si>
+    <t>04/05/12</t>
+  </si>
+  <si>
+    <t>bctgm040512pr.html</t>
+  </si>
+  <si>
+    <t>Bakery, Confectionery, Tobacco Workers and Grain Millers (BCTGM) 04/05/12</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>AFL-CIO</t>
+  </si>
+  <si>
+    <t>03/13/12</t>
+  </si>
+  <si>
+    <t>aflcio031312pr.html</t>
+  </si>
+  <si>
+    <t>AFL-CIO 03/13/12</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>International Brotherhood of Boilermakers (IBB)</t>
+  </si>
+  <si>
+    <t>03/09/12</t>
+  </si>
+  <si>
+    <t>ibb030912pr.html</t>
+  </si>
+  <si>
+    <t>International Brotherhood of Boilermakers (IBB) 03/09/12</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Laborers International Union of North America (LIUNA)</t>
+  </si>
+  <si>
+    <t>03/08/12</t>
+  </si>
+  <si>
+    <t>https://www.p2012.org/interestg/liuna030812pr.html</t>
+  </si>
+  <si>
+    <t>Laborers International Union of North America (LIUNA) 03/08/12</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>United Steelworkers (USW)</t>
+  </si>
+  <si>
+    <t>03/06/12</t>
+  </si>
+  <si>
+    <t>https://www.p2012.org/interestg/usw030612pr.html</t>
+  </si>
+  <si>
+    <t>United Steelworkers (USW) 03/06/12</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>United Association of Journeymen and Apprentices of the Plumbing and Pipefitting Industry (UA)</t>
+  </si>
+  <si>
+    <t>03/01/12</t>
+  </si>
+  <si>
+    <t>ua030112pr.html</t>
+  </si>
+  <si>
+    <t>United Association of Journeymen and Apprentices of the Plumbing and Pipefitting Industry (UA) 03/01/12</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>International Association of Machinists (IAM)</t>
+  </si>
+  <si>
+    <t>02/24/12</t>
+  </si>
+  <si>
+    <t>iam022412pr.html</t>
+  </si>
+  <si>
+    <t>International Association of Machinists (IAM) 02/24/12</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>American Federation of Teachers (AFT)</t>
+  </si>
+  <si>
+    <t>02/07/12</t>
+  </si>
+  <si>
+    <t>aft020712pr.html</t>
+  </si>
+  <si>
+    <t>American Federation of Teachers (AFT) 02/07/12</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Communications Workers of America (CWA)</t>
+  </si>
+  <si>
+    <t>02/02/12</t>
+  </si>
+  <si>
+    <t>cwa020212pr.html</t>
+  </si>
+  <si>
+    <t>Communications Workers of America (CWA) 02/02/12</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>United Farm Workers (UFW)</t>
+  </si>
+  <si>
+    <t>01/12/12</t>
+  </si>
+  <si>
+    <t>https://www.p2012.org/interestg/ufw011212pr.html</t>
+  </si>
+  <si>
+    <t>United Farm Workers (UFW) 01/12/12</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>American Federation of State, County and Municipal Employees (AFSCME)</t>
+  </si>
+  <si>
+    <t>12/06/11</t>
+  </si>
+  <si>
+    <t>afscme120611pr.html</t>
+  </si>
+  <si>
+    <t>American Federation of State, County and Municipal Employees (AFSCME) 12/06/11</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Retail, Wholesale and Department Store Union UFCW (RWDSU)</t>
+  </si>
+  <si>
+    <t>11/17/11</t>
+  </si>
+  <si>
+    <t>../../interestg/rwdsu111711pr.html</t>
+  </si>
+  <si>
+    <t>Retail, Wholesale and Department Store Union UFCW (RWDSU) 11/17/11</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Service Employees International Union (SEIU)</t>
+  </si>
+  <si>
+    <t>11/16/11</t>
+  </si>
+  <si>
+    <t>https://www.p2012.org/interestg/seiu111611pr.html</t>
+  </si>
+  <si>
+    <t>Service Employees International Union (SEIU) 11/16/11</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>United Food and Commercial Workers Union (UFCW)</t>
+  </si>
+  <si>
+    <t>10/20/11</t>
+  </si>
+  <si>
+    <t>ufcw102011pr.html</t>
+  </si>
+  <si>
+    <t>United Food and Commercial Workers Union (UFCW) 10/20/11</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>National Education Association (NEA)</t>
+  </si>
+  <si>
+    <t>07/04/11</t>
+  </si>
+  <si>
+    <t>../../interestg/nea070411pr.html</t>
+  </si>
+  <si>
+    <t>National Education Association (NEA) 07/04/11</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>2012R</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Mitt Romney</t>
+  </si>
+  <si>
+    <t>Log Cabin Republicans</t>
+  </si>
+  <si>
+    <t>10/23/12</t>
+  </si>
+  <si>
+    <t>logcabin102312pr.html</t>
+  </si>
+  <si>
+    <t>Log Cabin Republicans 10/23/12</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>National Rifle Association Political Victory Fund</t>
+  </si>
+  <si>
+    <t>10/04/12</t>
+  </si>
+  <si>
+    <t>nrapvf100412pr.html</t>
+  </si>
+  <si>
+    <t>National Rifle Association Political Victory Fund 10/04/12</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>CatholicVote.org</t>
+  </si>
+  <si>
+    <t>08/13/12</t>
+  </si>
+  <si>
+    <t>catholicvoteorg081312pr.html</t>
+  </si>
+  <si>
+    <t>CatholicVote.org 08/13/12</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>GOProud</t>
+  </si>
+  <si>
+    <t>06/20/12</t>
+  </si>
+  <si>
+    <t>goproud062012pr.html</t>
+  </si>
+  <si>
+    <t>GOProud 06/20/12</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>National Right to LIfe</t>
+  </si>
+  <si>
+    <t>04/12/12</t>
+  </si>
+  <si>
+    <t>nrtl041212pr.html</t>
+  </si>
+  <si>
+    <t>National Right to LIfe 04/12/12</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>Susan B. Anthony List</t>
+  </si>
+  <si>
+    <t>sbalist041212pr.html</t>
+  </si>
+  <si>
+    <t>Susan B. Anthony List 04/12/12</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>National Organization for Marriage</t>
+  </si>
+  <si>
+    <t>04/11/12</t>
+  </si>
+  <si>
+    <t>nom041112pr.html</t>
+  </si>
+  <si>
+    <t>National Organization for Marriage 04/11/12</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>Associated Builders and Contractors</t>
+  </si>
+  <si>
+    <t>02/22/12</t>
+  </si>
+  <si>
+    <t>abc022212pr.html</t>
+  </si>
+  <si>
+    <t>Associated Builders and Contractors 02/22/12</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Newt Gingrich</t>
+  </si>
+  <si>
+    <t>The Campaign to Defeat Barack Obama</t>
+  </si>
+  <si>
+    <t>01/29/12</t>
+  </si>
+  <si>
+    <t>campaigntodefeat012912pr.html</t>
+  </si>
+  <si>
+    <t>The Campaign to Defeat Barack Obama 01/29/12</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Rick Santorum</t>
+  </si>
+  <si>
+    <t>02/17/12</t>
+  </si>
+  <si>
+    <t>sbalist021712pr.html</t>
+  </si>
+  <si>
+    <t>Susan B. Anthony List 02/17/12</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>01/05/12</t>
+  </si>
+  <si>
+    <t>catholicvoteorg010512pr.html</t>
+  </si>
+  <si>
+    <t>CatholicVote.org 01/05/12</t>
+  </si>
+  <si>
+    <t>new-1</t>
+  </si>
+  <si>
+    <t>new-2</t>
+  </si>
+  <si>
+    <t>new-3</t>
+  </si>
+  <si>
+    <t>League of Conservation Voters</t>
+  </si>
+  <si>
+    <t>Environment Action</t>
+  </si>
+  <si>
+    <t>Clean Water Action</t>
+  </si>
+  <si>
+    <t>Sierra Club</t>
+  </si>
+  <si>
+    <t>added</t>
+  </si>
+  <si>
+    <t>parsed endorser_name from row 7</t>
+  </si>
+  <si>
+    <t>edited</t>
+  </si>
+  <si>
+    <t>parsed endorser_name into 4 rows</t>
+  </si>
+  <si>
+    <t>source typo: "Life" as on page</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="@"/>
-    <numFmt numFmtId="166" formatCode="@"/>
-  </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -751,12 +788,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <b/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -781,13 +820,22 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1069,32 +1117,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S246"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="14.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="40.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="8.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="8.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="15.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="40.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="23.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="21.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="8.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="10.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="10.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="8.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="18.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="18.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="40.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="11.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="80.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="40.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="6" width="8.6640625" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" customWidth="1"/>
+    <col min="8" max="8" width="40.6640625" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" customWidth="1"/>
+    <col min="10" max="10" width="21.6640625" customWidth="1"/>
+    <col min="11" max="11" width="8.6640625" customWidth="1"/>
+    <col min="12" max="13" width="10.6640625" customWidth="1"/>
+    <col min="14" max="14" width="8.6640625" customWidth="1"/>
+    <col min="15" max="16" width="18.6640625" customWidth="1"/>
+    <col min="17" max="17" width="40.6640625" customWidth="1"/>
+    <col min="18" max="18" width="11.6640625" customWidth="1"/>
+    <col min="19" max="19" width="80.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1153,7 +1198,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -1200,7 +1245,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
@@ -1247,7 +1292,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>36</v>
       </c>
@@ -1294,7 +1339,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>40</v>
       </c>
@@ -1341,7 +1386,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>45</v>
       </c>
@@ -1388,7 +1433,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>50</v>
       </c>
@@ -1435,15 +1480,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>247</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>21</v>
@@ -1458,7 +1503,7 @@
         <v>24</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>56</v>
+        <v>243</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>26</v>
@@ -1467,30 +1512,30 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R8" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>60</v>
+        <v>237</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>244</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>20</v>
+        <v>245</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>21</v>
@@ -1505,7 +1550,7 @@
         <v>24</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>61</v>
+        <v>240</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>26</v>
@@ -1514,30 +1559,28 @@
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="R9" s="1"/>
       <c r="S9" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>65</v>
+        <v>238</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>244</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>245</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>21</v>
@@ -1552,39 +1595,37 @@
         <v>24</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>66</v>
+        <v>241</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="R10" s="1"/>
       <c r="S10" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>71</v>
+        <v>239</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>244</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>20</v>
+        <v>245</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>21</v>
@@ -1599,33 +1640,31 @@
         <v>24</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>72</v>
+        <v>242</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="R11" s="1"/>
       <c r="S11" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>20</v>
@@ -1646,33 +1685,33 @@
         <v>24</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>20</v>
@@ -1693,33 +1732,33 @@
         <v>24</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="R13" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>20</v>
@@ -1740,33 +1779,33 @@
         <v>24</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="R14" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>20</v>
@@ -1787,33 +1826,33 @@
         <v>24</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>20</v>
@@ -1834,33 +1873,33 @@
         <v>24</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="R16" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>20</v>
@@ -1881,33 +1920,33 @@
         <v>24</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="R17" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>20</v>
@@ -1928,33 +1967,33 @@
         <v>24</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="R18" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>20</v>
@@ -1975,33 +2014,33 @@
         <v>24</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="R19" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>20</v>
@@ -2022,33 +2061,33 @@
         <v>24</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>20</v>
@@ -2069,33 +2108,33 @@
         <v>24</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>20</v>
@@ -2116,33 +2155,33 @@
         <v>24</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>20</v>
@@ -2163,33 +2202,33 @@
         <v>24</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>20</v>
@@ -2210,33 +2249,33 @@
         <v>24</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="R24" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>20</v>
@@ -2257,33 +2296,33 @@
         <v>24</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>20</v>
@@ -2304,33 +2343,33 @@
         <v>24</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>20</v>
@@ -2351,33 +2390,33 @@
         <v>24</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>20</v>
@@ -2398,33 +2437,33 @@
         <v>24</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>20</v>
@@ -2445,33 +2484,33 @@
         <v>24</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>20</v>
@@ -2492,33 +2531,33 @@
         <v>24</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>20</v>
@@ -2539,33 +2578,33 @@
         <v>24</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>20</v>
@@ -2586,33 +2625,33 @@
         <v>24</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>20</v>
@@ -2621,45 +2660,45 @@
         <v>20</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>184</v>
+        <v>24</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="R33" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>20</v>
@@ -2668,45 +2707,45 @@
         <v>20</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>184</v>
+        <v>24</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="R34" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>20</v>
@@ -2715,45 +2754,45 @@
         <v>20</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>184</v>
+        <v>24</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>20</v>
@@ -2762,19 +2801,19 @@
         <v>20</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F36" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="H36" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>26</v>
@@ -2783,24 +2822,24 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="R36" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S36" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>20</v>
@@ -2809,19 +2848,19 @@
         <v>20</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F37" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="H37" s="1" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>26</v>
@@ -2830,24 +2869,24 @@
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="R37" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>20</v>
@@ -2856,19 +2895,19 @@
         <v>20</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F38" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="H38" s="1" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>26</v>
@@ -2877,24 +2916,24 @@
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="R38" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>20</v>
@@ -2903,19 +2942,19 @@
         <v>20</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F39" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="H39" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>26</v>
@@ -2924,45 +2963,43 @@
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="1" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S39" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="B40" s="1"/>
       <c r="C40" s="1" t="s">
-        <v>20</v>
+        <v>248</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F40" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="H40" s="1" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>26</v>
@@ -2971,24 +3008,24 @@
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="R40" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>20</v>
@@ -2997,19 +3034,19 @@
         <v>20</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F41" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="H41" s="1" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>26</v>
@@ -3018,24 +3055,24 @@
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="R41" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S41" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>20</v>
@@ -3044,19 +3081,19 @@
         <v>20</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F42" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="H42" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>26</v>
@@ -3065,24 +3102,24 @@
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="R42" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>20</v>
@@ -3091,19 +3128,19 @@
         <v>20</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F43" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="H43" s="1" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>26</v>
@@ -3112,85 +3149,163 @@
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="R43" s="1" t="s">
         <v>29</v>
       </c>
       <c r="S43" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
+        <v>221</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
+      <c r="M44" s="1" t="s">
+        <v>225</v>
+      </c>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
-      <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
+      <c r="Q44" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="R44" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S44" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
+      <c r="M45" s="1" t="s">
+        <v>230</v>
+      </c>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
-      <c r="Q45" s="1"/>
-      <c r="R45" s="1"/>
-      <c r="S45" s="1"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
+      <c r="Q45" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="R45" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S45" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
+      <c r="M46" s="1" t="s">
+        <v>234</v>
+      </c>
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
-      <c r="Q46" s="1"/>
-      <c r="R46" s="1"/>
-      <c r="S46" s="1"/>
-    </row>
-    <row r="47">
+      <c r="Q46" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="R46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S46" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -3211,7 +3326,7 @@
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -3232,7 +3347,7 @@
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -3253,7 +3368,7 @@
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -3274,7 +3389,7 @@
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -3295,7 +3410,7 @@
       <c r="R51" s="1"/>
       <c r="S51" s="1"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -3316,7 +3431,7 @@
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -3337,7 +3452,7 @@
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -3358,7 +3473,7 @@
       <c r="R54" s="1"/>
       <c r="S54" s="1"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -3379,7 +3494,7 @@
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -3400,7 +3515,7 @@
       <c r="R56" s="1"/>
       <c r="S56" s="1"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -3421,7 +3536,7 @@
       <c r="R57" s="1"/>
       <c r="S57" s="1"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -3442,7 +3557,7 @@
       <c r="R58" s="1"/>
       <c r="S58" s="1"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -3463,7 +3578,7 @@
       <c r="R59" s="1"/>
       <c r="S59" s="1"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -3484,7 +3599,7 @@
       <c r="R60" s="1"/>
       <c r="S60" s="1"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -3505,7 +3620,7 @@
       <c r="R61" s="1"/>
       <c r="S61" s="1"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -3526,7 +3641,7 @@
       <c r="R62" s="1"/>
       <c r="S62" s="1"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -3547,7 +3662,7 @@
       <c r="R63" s="1"/>
       <c r="S63" s="1"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -3568,7 +3683,7 @@
       <c r="R64" s="1"/>
       <c r="S64" s="1"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -3589,7 +3704,7 @@
       <c r="R65" s="1"/>
       <c r="S65" s="1"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -3610,7 +3725,7 @@
       <c r="R66" s="1"/>
       <c r="S66" s="1"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -3631,7 +3746,7 @@
       <c r="R67" s="1"/>
       <c r="S67" s="1"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -3652,7 +3767,7 @@
       <c r="R68" s="1"/>
       <c r="S68" s="1"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -3673,7 +3788,7 @@
       <c r="R69" s="1"/>
       <c r="S69" s="1"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -3694,7 +3809,7 @@
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -3715,7 +3830,7 @@
       <c r="R71" s="1"/>
       <c r="S71" s="1"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3736,7 +3851,7 @@
       <c r="R72" s="1"/>
       <c r="S72" s="1"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -3757,7 +3872,7 @@
       <c r="R73" s="1"/>
       <c r="S73" s="1"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3778,7 +3893,7 @@
       <c r="R74" s="1"/>
       <c r="S74" s="1"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3799,7 +3914,7 @@
       <c r="R75" s="1"/>
       <c r="S75" s="1"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3820,7 +3935,7 @@
       <c r="R76" s="1"/>
       <c r="S76" s="1"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -3841,7 +3956,7 @@
       <c r="R77" s="1"/>
       <c r="S77" s="1"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3862,7 +3977,7 @@
       <c r="R78" s="1"/>
       <c r="S78" s="1"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3883,7 +3998,7 @@
       <c r="R79" s="1"/>
       <c r="S79" s="1"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3904,7 +4019,7 @@
       <c r="R80" s="1"/>
       <c r="S80" s="1"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3925,7 +4040,7 @@
       <c r="R81" s="1"/>
       <c r="S81" s="1"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3946,7 +4061,7 @@
       <c r="R82" s="1"/>
       <c r="S82" s="1"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3967,7 +4082,7 @@
       <c r="R83" s="1"/>
       <c r="S83" s="1"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3988,7 +4103,7 @@
       <c r="R84" s="1"/>
       <c r="S84" s="1"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -4009,7 +4124,7 @@
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -4030,7 +4145,7 @@
       <c r="R86" s="1"/>
       <c r="S86" s="1"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -4051,7 +4166,7 @@
       <c r="R87" s="1"/>
       <c r="S87" s="1"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -4072,7 +4187,7 @@
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -4093,7 +4208,7 @@
       <c r="R89" s="1"/>
       <c r="S89" s="1"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -4114,7 +4229,7 @@
       <c r="R90" s="1"/>
       <c r="S90" s="1"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -4135,7 +4250,7 @@
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
     </row>
-    <row r="92">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -4156,7 +4271,7 @@
       <c r="R92" s="1"/>
       <c r="S92" s="1"/>
     </row>
-    <row r="93">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -4177,7 +4292,7 @@
       <c r="R93" s="1"/>
       <c r="S93" s="1"/>
     </row>
-    <row r="94">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -4198,7 +4313,7 @@
       <c r="R94" s="1"/>
       <c r="S94" s="1"/>
     </row>
-    <row r="95">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -4219,7 +4334,7 @@
       <c r="R95" s="1"/>
       <c r="S95" s="1"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -4240,7 +4355,7 @@
       <c r="R96" s="1"/>
       <c r="S96" s="1"/>
     </row>
-    <row r="97">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -4261,7 +4376,7 @@
       <c r="R97" s="1"/>
       <c r="S97" s="1"/>
     </row>
-    <row r="98">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -4282,7 +4397,7 @@
       <c r="R98" s="1"/>
       <c r="S98" s="1"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -4303,7 +4418,7 @@
       <c r="R99" s="1"/>
       <c r="S99" s="1"/>
     </row>
-    <row r="100">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -4324,7 +4439,7 @@
       <c r="R100" s="1"/>
       <c r="S100" s="1"/>
     </row>
-    <row r="101">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -4345,7 +4460,7 @@
       <c r="R101" s="1"/>
       <c r="S101" s="1"/>
     </row>
-    <row r="102">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -4366,7 +4481,7 @@
       <c r="R102" s="1"/>
       <c r="S102" s="1"/>
     </row>
-    <row r="103">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -4387,7 +4502,7 @@
       <c r="R103" s="1"/>
       <c r="S103" s="1"/>
     </row>
-    <row r="104">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -4408,7 +4523,7 @@
       <c r="R104" s="1"/>
       <c r="S104" s="1"/>
     </row>
-    <row r="105">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -4429,7 +4544,7 @@
       <c r="R105" s="1"/>
       <c r="S105" s="1"/>
     </row>
-    <row r="106">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -4450,7 +4565,7 @@
       <c r="R106" s="1"/>
       <c r="S106" s="1"/>
     </row>
-    <row r="107">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -4471,7 +4586,7 @@
       <c r="R107" s="1"/>
       <c r="S107" s="1"/>
     </row>
-    <row r="108">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -4492,7 +4607,7 @@
       <c r="R108" s="1"/>
       <c r="S108" s="1"/>
     </row>
-    <row r="109">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -4513,7 +4628,7 @@
       <c r="R109" s="1"/>
       <c r="S109" s="1"/>
     </row>
-    <row r="110">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -4534,7 +4649,7 @@
       <c r="R110" s="1"/>
       <c r="S110" s="1"/>
     </row>
-    <row r="111">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -4555,7 +4670,7 @@
       <c r="R111" s="1"/>
       <c r="S111" s="1"/>
     </row>
-    <row r="112">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -4576,7 +4691,7 @@
       <c r="R112" s="1"/>
       <c r="S112" s="1"/>
     </row>
-    <row r="113">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -4597,7 +4712,7 @@
       <c r="R113" s="1"/>
       <c r="S113" s="1"/>
     </row>
-    <row r="114">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -4618,7 +4733,7 @@
       <c r="R114" s="1"/>
       <c r="S114" s="1"/>
     </row>
-    <row r="115">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -4639,7 +4754,7 @@
       <c r="R115" s="1"/>
       <c r="S115" s="1"/>
     </row>
-    <row r="116">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -4660,7 +4775,7 @@
       <c r="R116" s="1"/>
       <c r="S116" s="1"/>
     </row>
-    <row r="117">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -4681,7 +4796,7 @@
       <c r="R117" s="1"/>
       <c r="S117" s="1"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -4702,7 +4817,7 @@
       <c r="R118" s="1"/>
       <c r="S118" s="1"/>
     </row>
-    <row r="119">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -4723,7 +4838,7 @@
       <c r="R119" s="1"/>
       <c r="S119" s="1"/>
     </row>
-    <row r="120">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4744,7 +4859,7 @@
       <c r="R120" s="1"/>
       <c r="S120" s="1"/>
     </row>
-    <row r="121">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4765,7 +4880,7 @@
       <c r="R121" s="1"/>
       <c r="S121" s="1"/>
     </row>
-    <row r="122">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4786,7 +4901,7 @@
       <c r="R122" s="1"/>
       <c r="S122" s="1"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4807,7 +4922,7 @@
       <c r="R123" s="1"/>
       <c r="S123" s="1"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -4828,7 +4943,7 @@
       <c r="R124" s="1"/>
       <c r="S124" s="1"/>
     </row>
-    <row r="125">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -4849,7 +4964,7 @@
       <c r="R125" s="1"/>
       <c r="S125" s="1"/>
     </row>
-    <row r="126">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -4870,7 +4985,7 @@
       <c r="R126" s="1"/>
       <c r="S126" s="1"/>
     </row>
-    <row r="127">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -4891,7 +5006,7 @@
       <c r="R127" s="1"/>
       <c r="S127" s="1"/>
     </row>
-    <row r="128">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -4912,7 +5027,7 @@
       <c r="R128" s="1"/>
       <c r="S128" s="1"/>
     </row>
-    <row r="129">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4933,7 +5048,7 @@
       <c r="R129" s="1"/>
       <c r="S129" s="1"/>
     </row>
-    <row r="130">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4954,7 +5069,7 @@
       <c r="R130" s="1"/>
       <c r="S130" s="1"/>
     </row>
-    <row r="131">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4975,7 +5090,7 @@
       <c r="R131" s="1"/>
       <c r="S131" s="1"/>
     </row>
-    <row r="132">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4996,7 +5111,7 @@
       <c r="R132" s="1"/>
       <c r="S132" s="1"/>
     </row>
-    <row r="133">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -5017,7 +5132,7 @@
       <c r="R133" s="1"/>
       <c r="S133" s="1"/>
     </row>
-    <row r="134">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -5038,7 +5153,7 @@
       <c r="R134" s="1"/>
       <c r="S134" s="1"/>
     </row>
-    <row r="135">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -5059,7 +5174,7 @@
       <c r="R135" s="1"/>
       <c r="S135" s="1"/>
     </row>
-    <row r="136">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -5080,7 +5195,7 @@
       <c r="R136" s="1"/>
       <c r="S136" s="1"/>
     </row>
-    <row r="137">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -5101,7 +5216,7 @@
       <c r="R137" s="1"/>
       <c r="S137" s="1"/>
     </row>
-    <row r="138">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -5122,7 +5237,7 @@
       <c r="R138" s="1"/>
       <c r="S138" s="1"/>
     </row>
-    <row r="139">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -5143,7 +5258,7 @@
       <c r="R139" s="1"/>
       <c r="S139" s="1"/>
     </row>
-    <row r="140">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -5164,7 +5279,7 @@
       <c r="R140" s="1"/>
       <c r="S140" s="1"/>
     </row>
-    <row r="141">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -5185,7 +5300,7 @@
       <c r="R141" s="1"/>
       <c r="S141" s="1"/>
     </row>
-    <row r="142">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -5206,7 +5321,7 @@
       <c r="R142" s="1"/>
       <c r="S142" s="1"/>
     </row>
-    <row r="143">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -5227,7 +5342,7 @@
       <c r="R143" s="1"/>
       <c r="S143" s="1"/>
     </row>
-    <row r="144">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -5248,7 +5363,7 @@
       <c r="R144" s="1"/>
       <c r="S144" s="1"/>
     </row>
-    <row r="145">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -5269,7 +5384,7 @@
       <c r="R145" s="1"/>
       <c r="S145" s="1"/>
     </row>
-    <row r="146">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -5290,7 +5405,7 @@
       <c r="R146" s="1"/>
       <c r="S146" s="1"/>
     </row>
-    <row r="147">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -5311,7 +5426,7 @@
       <c r="R147" s="1"/>
       <c r="S147" s="1"/>
     </row>
-    <row r="148">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -5332,7 +5447,7 @@
       <c r="R148" s="1"/>
       <c r="S148" s="1"/>
     </row>
-    <row r="149">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -5353,7 +5468,7 @@
       <c r="R149" s="1"/>
       <c r="S149" s="1"/>
     </row>
-    <row r="150">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -5374,7 +5489,7 @@
       <c r="R150" s="1"/>
       <c r="S150" s="1"/>
     </row>
-    <row r="151">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -5395,7 +5510,7 @@
       <c r="R151" s="1"/>
       <c r="S151" s="1"/>
     </row>
-    <row r="152">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -5416,7 +5531,7 @@
       <c r="R152" s="1"/>
       <c r="S152" s="1"/>
     </row>
-    <row r="153">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -5437,7 +5552,7 @@
       <c r="R153" s="1"/>
       <c r="S153" s="1"/>
     </row>
-    <row r="154">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -5458,7 +5573,7 @@
       <c r="R154" s="1"/>
       <c r="S154" s="1"/>
     </row>
-    <row r="155">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -5479,7 +5594,7 @@
       <c r="R155" s="1"/>
       <c r="S155" s="1"/>
     </row>
-    <row r="156">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -5500,7 +5615,7 @@
       <c r="R156" s="1"/>
       <c r="S156" s="1"/>
     </row>
-    <row r="157">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -5521,7 +5636,7 @@
       <c r="R157" s="1"/>
       <c r="S157" s="1"/>
     </row>
-    <row r="158">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -5542,7 +5657,7 @@
       <c r="R158" s="1"/>
       <c r="S158" s="1"/>
     </row>
-    <row r="159">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -5563,7 +5678,7 @@
       <c r="R159" s="1"/>
       <c r="S159" s="1"/>
     </row>
-    <row r="160">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -5584,7 +5699,7 @@
       <c r="R160" s="1"/>
       <c r="S160" s="1"/>
     </row>
-    <row r="161">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -5605,7 +5720,7 @@
       <c r="R161" s="1"/>
       <c r="S161" s="1"/>
     </row>
-    <row r="162">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -5626,7 +5741,7 @@
       <c r="R162" s="1"/>
       <c r="S162" s="1"/>
     </row>
-    <row r="163">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -5647,7 +5762,7 @@
       <c r="R163" s="1"/>
       <c r="S163" s="1"/>
     </row>
-    <row r="164">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -5668,7 +5783,7 @@
       <c r="R164" s="1"/>
       <c r="S164" s="1"/>
     </row>
-    <row r="165">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -5689,7 +5804,7 @@
       <c r="R165" s="1"/>
       <c r="S165" s="1"/>
     </row>
-    <row r="166">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -5710,7 +5825,7 @@
       <c r="R166" s="1"/>
       <c r="S166" s="1"/>
     </row>
-    <row r="167">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -5731,7 +5846,7 @@
       <c r="R167" s="1"/>
       <c r="S167" s="1"/>
     </row>
-    <row r="168">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -5752,7 +5867,7 @@
       <c r="R168" s="1"/>
       <c r="S168" s="1"/>
     </row>
-    <row r="169">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -5773,7 +5888,7 @@
       <c r="R169" s="1"/>
       <c r="S169" s="1"/>
     </row>
-    <row r="170">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -5794,7 +5909,7 @@
       <c r="R170" s="1"/>
       <c r="S170" s="1"/>
     </row>
-    <row r="171">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -5815,7 +5930,7 @@
       <c r="R171" s="1"/>
       <c r="S171" s="1"/>
     </row>
-    <row r="172">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -5836,7 +5951,7 @@
       <c r="R172" s="1"/>
       <c r="S172" s="1"/>
     </row>
-    <row r="173">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -5857,7 +5972,7 @@
       <c r="R173" s="1"/>
       <c r="S173" s="1"/>
     </row>
-    <row r="174">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -5878,7 +5993,7 @@
       <c r="R174" s="1"/>
       <c r="S174" s="1"/>
     </row>
-    <row r="175">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -5899,7 +6014,7 @@
       <c r="R175" s="1"/>
       <c r="S175" s="1"/>
     </row>
-    <row r="176">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -5920,7 +6035,7 @@
       <c r="R176" s="1"/>
       <c r="S176" s="1"/>
     </row>
-    <row r="177">
+    <row r="177" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -5941,7 +6056,7 @@
       <c r="R177" s="1"/>
       <c r="S177" s="1"/>
     </row>
-    <row r="178">
+    <row r="178" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -5962,7 +6077,7 @@
       <c r="R178" s="1"/>
       <c r="S178" s="1"/>
     </row>
-    <row r="179">
+    <row r="179" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -5983,7 +6098,7 @@
       <c r="R179" s="1"/>
       <c r="S179" s="1"/>
     </row>
-    <row r="180">
+    <row r="180" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -6004,7 +6119,7 @@
       <c r="R180" s="1"/>
       <c r="S180" s="1"/>
     </row>
-    <row r="181">
+    <row r="181" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -6025,7 +6140,7 @@
       <c r="R181" s="1"/>
       <c r="S181" s="1"/>
     </row>
-    <row r="182">
+    <row r="182" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -6046,7 +6161,7 @@
       <c r="R182" s="1"/>
       <c r="S182" s="1"/>
     </row>
-    <row r="183">
+    <row r="183" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -6067,7 +6182,7 @@
       <c r="R183" s="1"/>
       <c r="S183" s="1"/>
     </row>
-    <row r="184">
+    <row r="184" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -6088,7 +6203,7 @@
       <c r="R184" s="1"/>
       <c r="S184" s="1"/>
     </row>
-    <row r="185">
+    <row r="185" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -6109,7 +6224,7 @@
       <c r="R185" s="1"/>
       <c r="S185" s="1"/>
     </row>
-    <row r="186">
+    <row r="186" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -6130,7 +6245,7 @@
       <c r="R186" s="1"/>
       <c r="S186" s="1"/>
     </row>
-    <row r="187">
+    <row r="187" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -6151,7 +6266,7 @@
       <c r="R187" s="1"/>
       <c r="S187" s="1"/>
     </row>
-    <row r="188">
+    <row r="188" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -6172,7 +6287,7 @@
       <c r="R188" s="1"/>
       <c r="S188" s="1"/>
     </row>
-    <row r="189">
+    <row r="189" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -6193,7 +6308,7 @@
       <c r="R189" s="1"/>
       <c r="S189" s="1"/>
     </row>
-    <row r="190">
+    <row r="190" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -6214,7 +6329,7 @@
       <c r="R190" s="1"/>
       <c r="S190" s="1"/>
     </row>
-    <row r="191">
+    <row r="191" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -6235,7 +6350,7 @@
       <c r="R191" s="1"/>
       <c r="S191" s="1"/>
     </row>
-    <row r="192">
+    <row r="192" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -6256,7 +6371,7 @@
       <c r="R192" s="1"/>
       <c r="S192" s="1"/>
     </row>
-    <row r="193">
+    <row r="193" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -6277,7 +6392,7 @@
       <c r="R193" s="1"/>
       <c r="S193" s="1"/>
     </row>
-    <row r="194">
+    <row r="194" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -6298,7 +6413,7 @@
       <c r="R194" s="1"/>
       <c r="S194" s="1"/>
     </row>
-    <row r="195">
+    <row r="195" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -6319,7 +6434,7 @@
       <c r="R195" s="1"/>
       <c r="S195" s="1"/>
     </row>
-    <row r="196">
+    <row r="196" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -6340,7 +6455,7 @@
       <c r="R196" s="1"/>
       <c r="S196" s="1"/>
     </row>
-    <row r="197">
+    <row r="197" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -6361,7 +6476,7 @@
       <c r="R197" s="1"/>
       <c r="S197" s="1"/>
     </row>
-    <row r="198">
+    <row r="198" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -6382,7 +6497,7 @@
       <c r="R198" s="1"/>
       <c r="S198" s="1"/>
     </row>
-    <row r="199">
+    <row r="199" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -6403,7 +6518,7 @@
       <c r="R199" s="1"/>
       <c r="S199" s="1"/>
     </row>
-    <row r="200">
+    <row r="200" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -6424,7 +6539,7 @@
       <c r="R200" s="1"/>
       <c r="S200" s="1"/>
     </row>
-    <row r="201">
+    <row r="201" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -6445,7 +6560,7 @@
       <c r="R201" s="1"/>
       <c r="S201" s="1"/>
     </row>
-    <row r="202">
+    <row r="202" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -6466,7 +6581,7 @@
       <c r="R202" s="1"/>
       <c r="S202" s="1"/>
     </row>
-    <row r="203">
+    <row r="203" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -6487,7 +6602,7 @@
       <c r="R203" s="1"/>
       <c r="S203" s="1"/>
     </row>
-    <row r="204">
+    <row r="204" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -6508,7 +6623,7 @@
       <c r="R204" s="1"/>
       <c r="S204" s="1"/>
     </row>
-    <row r="205">
+    <row r="205" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -6529,7 +6644,7 @@
       <c r="R205" s="1"/>
       <c r="S205" s="1"/>
     </row>
-    <row r="206">
+    <row r="206" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -6550,7 +6665,7 @@
       <c r="R206" s="1"/>
       <c r="S206" s="1"/>
     </row>
-    <row r="207">
+    <row r="207" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -6571,7 +6686,7 @@
       <c r="R207" s="1"/>
       <c r="S207" s="1"/>
     </row>
-    <row r="208">
+    <row r="208" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -6592,7 +6707,7 @@
       <c r="R208" s="1"/>
       <c r="S208" s="1"/>
     </row>
-    <row r="209">
+    <row r="209" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -6613,7 +6728,7 @@
       <c r="R209" s="1"/>
       <c r="S209" s="1"/>
     </row>
-    <row r="210">
+    <row r="210" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -6634,7 +6749,7 @@
       <c r="R210" s="1"/>
       <c r="S210" s="1"/>
     </row>
-    <row r="211">
+    <row r="211" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -6655,7 +6770,7 @@
       <c r="R211" s="1"/>
       <c r="S211" s="1"/>
     </row>
-    <row r="212">
+    <row r="212" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -6676,7 +6791,7 @@
       <c r="R212" s="1"/>
       <c r="S212" s="1"/>
     </row>
-    <row r="213">
+    <row r="213" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -6697,7 +6812,7 @@
       <c r="R213" s="1"/>
       <c r="S213" s="1"/>
     </row>
-    <row r="214">
+    <row r="214" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -6718,7 +6833,7 @@
       <c r="R214" s="1"/>
       <c r="S214" s="1"/>
     </row>
-    <row r="215">
+    <row r="215" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -6739,7 +6854,7 @@
       <c r="R215" s="1"/>
       <c r="S215" s="1"/>
     </row>
-    <row r="216">
+    <row r="216" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -6760,7 +6875,7 @@
       <c r="R216" s="1"/>
       <c r="S216" s="1"/>
     </row>
-    <row r="217">
+    <row r="217" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -6781,7 +6896,7 @@
       <c r="R217" s="1"/>
       <c r="S217" s="1"/>
     </row>
-    <row r="218">
+    <row r="218" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -6802,7 +6917,7 @@
       <c r="R218" s="1"/>
       <c r="S218" s="1"/>
     </row>
-    <row r="219">
+    <row r="219" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -6823,7 +6938,7 @@
       <c r="R219" s="1"/>
       <c r="S219" s="1"/>
     </row>
-    <row r="220">
+    <row r="220" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -6844,7 +6959,7 @@
       <c r="R220" s="1"/>
       <c r="S220" s="1"/>
     </row>
-    <row r="221">
+    <row r="221" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -6865,7 +6980,7 @@
       <c r="R221" s="1"/>
       <c r="S221" s="1"/>
     </row>
-    <row r="222">
+    <row r="222" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -6886,7 +7001,7 @@
       <c r="R222" s="1"/>
       <c r="S222" s="1"/>
     </row>
-    <row r="223">
+    <row r="223" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -6907,7 +7022,7 @@
       <c r="R223" s="1"/>
       <c r="S223" s="1"/>
     </row>
-    <row r="224">
+    <row r="224" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -6928,7 +7043,7 @@
       <c r="R224" s="1"/>
       <c r="S224" s="1"/>
     </row>
-    <row r="225">
+    <row r="225" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -6949,7 +7064,7 @@
       <c r="R225" s="1"/>
       <c r="S225" s="1"/>
     </row>
-    <row r="226">
+    <row r="226" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -6970,7 +7085,7 @@
       <c r="R226" s="1"/>
       <c r="S226" s="1"/>
     </row>
-    <row r="227">
+    <row r="227" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -6991,7 +7106,7 @@
       <c r="R227" s="1"/>
       <c r="S227" s="1"/>
     </row>
-    <row r="228">
+    <row r="228" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -7012,7 +7127,7 @@
       <c r="R228" s="1"/>
       <c r="S228" s="1"/>
     </row>
-    <row r="229">
+    <row r="229" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -7033,7 +7148,7 @@
       <c r="R229" s="1"/>
       <c r="S229" s="1"/>
     </row>
-    <row r="230">
+    <row r="230" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -7054,7 +7169,7 @@
       <c r="R230" s="1"/>
       <c r="S230" s="1"/>
     </row>
-    <row r="231">
+    <row r="231" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -7075,7 +7190,7 @@
       <c r="R231" s="1"/>
       <c r="S231" s="1"/>
     </row>
-    <row r="232">
+    <row r="232" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -7096,7 +7211,7 @@
       <c r="R232" s="1"/>
       <c r="S232" s="1"/>
     </row>
-    <row r="233">
+    <row r="233" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -7117,7 +7232,7 @@
       <c r="R233" s="1"/>
       <c r="S233" s="1"/>
     </row>
-    <row r="234">
+    <row r="234" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -7138,7 +7253,7 @@
       <c r="R234" s="1"/>
       <c r="S234" s="1"/>
     </row>
-    <row r="235">
+    <row r="235" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -7159,7 +7274,7 @@
       <c r="R235" s="1"/>
       <c r="S235" s="1"/>
     </row>
-    <row r="236">
+    <row r="236" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -7180,7 +7295,7 @@
       <c r="R236" s="1"/>
       <c r="S236" s="1"/>
     </row>
-    <row r="237">
+    <row r="237" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -7201,7 +7316,7 @@
       <c r="R237" s="1"/>
       <c r="S237" s="1"/>
     </row>
-    <row r="238">
+    <row r="238" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -7222,7 +7337,7 @@
       <c r="R238" s="1"/>
       <c r="S238" s="1"/>
     </row>
-    <row r="239">
+    <row r="239" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -7243,7 +7358,7 @@
       <c r="R239" s="1"/>
       <c r="S239" s="1"/>
     </row>
-    <row r="240">
+    <row r="240" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -7264,7 +7379,7 @@
       <c r="R240" s="1"/>
       <c r="S240" s="1"/>
     </row>
-    <row r="241">
+    <row r="241" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -7285,7 +7400,7 @@
       <c r="R241" s="1"/>
       <c r="S241" s="1"/>
     </row>
-    <row r="242">
+    <row r="242" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -7306,7 +7421,7 @@
       <c r="R242" s="1"/>
       <c r="S242" s="1"/>
     </row>
-    <row r="243">
+    <row r="243" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -7327,9 +7442,72 @@
       <c r="R243" s="1"/>
       <c r="S243" s="1"/>
     </row>
+    <row r="244" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A244" s="1"/>
+      <c r="B244" s="1"/>
+      <c r="C244" s="1"/>
+      <c r="D244" s="1"/>
+      <c r="E244" s="1"/>
+      <c r="F244" s="1"/>
+      <c r="G244" s="1"/>
+      <c r="H244" s="1"/>
+      <c r="I244" s="1"/>
+      <c r="J244" s="1"/>
+      <c r="K244" s="1"/>
+      <c r="L244" s="1"/>
+      <c r="M244" s="1"/>
+      <c r="N244" s="1"/>
+      <c r="O244" s="1"/>
+      <c r="P244" s="1"/>
+      <c r="Q244" s="1"/>
+      <c r="R244" s="1"/>
+      <c r="S244" s="1"/>
+    </row>
+    <row r="245" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A245" s="1"/>
+      <c r="B245" s="1"/>
+      <c r="C245" s="1"/>
+      <c r="D245" s="1"/>
+      <c r="E245" s="1"/>
+      <c r="F245" s="1"/>
+      <c r="G245" s="1"/>
+      <c r="H245" s="1"/>
+      <c r="I245" s="1"/>
+      <c r="J245" s="1"/>
+      <c r="K245" s="1"/>
+      <c r="L245" s="1"/>
+      <c r="M245" s="1"/>
+      <c r="N245" s="1"/>
+      <c r="O245" s="1"/>
+      <c r="P245" s="1"/>
+      <c r="Q245" s="1"/>
+      <c r="R245" s="1"/>
+      <c r="S245" s="1"/>
+    </row>
+    <row r="246" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A246" s="1"/>
+      <c r="B246" s="1"/>
+      <c r="C246" s="1"/>
+      <c r="D246" s="1"/>
+      <c r="E246" s="1"/>
+      <c r="F246" s="1"/>
+      <c r="G246" s="1"/>
+      <c r="H246" s="1"/>
+      <c r="I246" s="1"/>
+      <c r="J246" s="1"/>
+      <c r="K246" s="1"/>
+      <c r="L246" s="1"/>
+      <c r="M246" s="1"/>
+      <c r="N246" s="1"/>
+      <c r="O246" s="1"/>
+      <c r="P246" s="1"/>
+      <c r="Q246" s="1"/>
+      <c r="R246" s="1"/>
+      <c r="S246" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S43"/>
+  <autoFilter ref="A1:S46" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>